--- a/plantilla/finanzas-plantilla.xlsx
+++ b/plantilla/finanzas-plantilla.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1000"/>
+  <dimension ref="A1:H1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -444,6 +444,8 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,4004 +479,5018 @@
           <t>Registrado</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo Salario</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha Ingreso</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="D2" s="2" t="n"/>
       <c r="F2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="D3" s="2" t="n"/>
       <c r="F3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="D4" s="2" t="n"/>
       <c r="F4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="D5" s="2" t="n"/>
       <c r="F5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="D6" s="2" t="n"/>
       <c r="F6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="D7" s="2" t="n"/>
       <c r="F7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="D8" s="2" t="n"/>
       <c r="F8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="D9" s="2" t="n"/>
       <c r="F9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="D10" s="2" t="n"/>
       <c r="F10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="D11" s="2" t="n"/>
       <c r="F11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="D12" s="2" t="n"/>
       <c r="F12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="D13" s="2" t="n"/>
       <c r="F13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="D14" s="2" t="n"/>
       <c r="F14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="D15" s="2" t="n"/>
       <c r="F15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="D16" s="2" t="n"/>
       <c r="F16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="D17" s="2" t="n"/>
       <c r="F17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="D18" s="2" t="n"/>
       <c r="F18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="D19" s="2" t="n"/>
       <c r="F19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="D20" s="2" t="n"/>
       <c r="F20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="D21" s="2" t="n"/>
       <c r="F21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="D22" s="2" t="n"/>
       <c r="F22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="D23" s="2" t="n"/>
       <c r="F23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="D24" s="2" t="n"/>
       <c r="F24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="D25" s="2" t="n"/>
       <c r="F25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="D26" s="2" t="n"/>
       <c r="F26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="D27" s="2" t="n"/>
       <c r="F27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="D28" s="2" t="n"/>
       <c r="F28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="D29" s="2" t="n"/>
       <c r="F29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="D30" s="2" t="n"/>
       <c r="F30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="D31" s="2" t="n"/>
       <c r="F31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="D32" s="2" t="n"/>
       <c r="F32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="D33" s="2" t="n"/>
       <c r="F33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="D34" s="2" t="n"/>
       <c r="F34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="D35" s="2" t="n"/>
       <c r="F35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="D36" s="2" t="n"/>
       <c r="F36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="D37" s="2" t="n"/>
       <c r="F37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="D38" s="2" t="n"/>
       <c r="F38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="D39" s="2" t="n"/>
       <c r="F39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="D40" s="2" t="n"/>
       <c r="F40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="D41" s="2" t="n"/>
       <c r="F41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="D42" s="2" t="n"/>
       <c r="F42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="D43" s="2" t="n"/>
       <c r="F43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="D44" s="2" t="n"/>
       <c r="F44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="D45" s="2" t="n"/>
       <c r="F45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="D46" s="2" t="n"/>
       <c r="F46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="D47" s="2" t="n"/>
       <c r="F47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="D48" s="2" t="n"/>
       <c r="F48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="D49" s="2" t="n"/>
       <c r="F49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="D50" s="2" t="n"/>
       <c r="F50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="D51" s="2" t="n"/>
       <c r="F51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="D52" s="2" t="n"/>
       <c r="F52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="D53" s="2" t="n"/>
       <c r="F53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="D54" s="2" t="n"/>
       <c r="F54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="D55" s="2" t="n"/>
       <c r="F55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="D56" s="2" t="n"/>
       <c r="F56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="D57" s="2" t="n"/>
       <c r="F57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="D58" s="2" t="n"/>
       <c r="F58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="D59" s="2" t="n"/>
       <c r="F59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="D60" s="2" t="n"/>
       <c r="F60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="D61" s="2" t="n"/>
       <c r="F61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="D62" s="2" t="n"/>
       <c r="F62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="D63" s="2" t="n"/>
       <c r="F63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
     </row>
     <row r="64">
       <c r="D64" s="2" t="n"/>
       <c r="F64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
     </row>
     <row r="65">
       <c r="D65" s="2" t="n"/>
       <c r="F65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
     </row>
     <row r="66">
       <c r="D66" s="2" t="n"/>
       <c r="F66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
     </row>
     <row r="67">
       <c r="D67" s="2" t="n"/>
       <c r="F67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
     </row>
     <row r="68">
       <c r="D68" s="2" t="n"/>
       <c r="F68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
     </row>
     <row r="69">
       <c r="D69" s="2" t="n"/>
       <c r="F69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
     </row>
     <row r="70">
       <c r="D70" s="2" t="n"/>
       <c r="F70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
     </row>
     <row r="71">
       <c r="D71" s="2" t="n"/>
       <c r="F71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
     </row>
     <row r="72">
       <c r="D72" s="2" t="n"/>
       <c r="F72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
     </row>
     <row r="73">
       <c r="D73" s="2" t="n"/>
       <c r="F73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
     </row>
     <row r="74">
       <c r="D74" s="2" t="n"/>
       <c r="F74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
     </row>
     <row r="75">
       <c r="D75" s="2" t="n"/>
       <c r="F75" s="3" t="n"/>
+      <c r="H75" s="3" t="n"/>
     </row>
     <row r="76">
       <c r="D76" s="2" t="n"/>
       <c r="F76" s="3" t="n"/>
+      <c r="H76" s="3" t="n"/>
     </row>
     <row r="77">
       <c r="D77" s="2" t="n"/>
       <c r="F77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
     </row>
     <row r="78">
       <c r="D78" s="2" t="n"/>
       <c r="F78" s="3" t="n"/>
+      <c r="H78" s="3" t="n"/>
     </row>
     <row r="79">
       <c r="D79" s="2" t="n"/>
       <c r="F79" s="3" t="n"/>
+      <c r="H79" s="3" t="n"/>
     </row>
     <row r="80">
       <c r="D80" s="2" t="n"/>
       <c r="F80" s="3" t="n"/>
+      <c r="H80" s="3" t="n"/>
     </row>
     <row r="81">
       <c r="D81" s="2" t="n"/>
       <c r="F81" s="3" t="n"/>
+      <c r="H81" s="3" t="n"/>
     </row>
     <row r="82">
       <c r="D82" s="2" t="n"/>
       <c r="F82" s="3" t="n"/>
+      <c r="H82" s="3" t="n"/>
     </row>
     <row r="83">
       <c r="D83" s="2" t="n"/>
       <c r="F83" s="3" t="n"/>
+      <c r="H83" s="3" t="n"/>
     </row>
     <row r="84">
       <c r="D84" s="2" t="n"/>
       <c r="F84" s="3" t="n"/>
+      <c r="H84" s="3" t="n"/>
     </row>
     <row r="85">
       <c r="D85" s="2" t="n"/>
       <c r="F85" s="3" t="n"/>
+      <c r="H85" s="3" t="n"/>
     </row>
     <row r="86">
       <c r="D86" s="2" t="n"/>
       <c r="F86" s="3" t="n"/>
+      <c r="H86" s="3" t="n"/>
     </row>
     <row r="87">
       <c r="D87" s="2" t="n"/>
       <c r="F87" s="3" t="n"/>
+      <c r="H87" s="3" t="n"/>
     </row>
     <row r="88">
       <c r="D88" s="2" t="n"/>
       <c r="F88" s="3" t="n"/>
+      <c r="H88" s="3" t="n"/>
     </row>
     <row r="89">
       <c r="D89" s="2" t="n"/>
       <c r="F89" s="3" t="n"/>
+      <c r="H89" s="3" t="n"/>
     </row>
     <row r="90">
       <c r="D90" s="2" t="n"/>
       <c r="F90" s="3" t="n"/>
+      <c r="H90" s="3" t="n"/>
     </row>
     <row r="91">
       <c r="D91" s="2" t="n"/>
       <c r="F91" s="3" t="n"/>
+      <c r="H91" s="3" t="n"/>
     </row>
     <row r="92">
       <c r="D92" s="2" t="n"/>
       <c r="F92" s="3" t="n"/>
+      <c r="H92" s="3" t="n"/>
     </row>
     <row r="93">
       <c r="D93" s="2" t="n"/>
       <c r="F93" s="3" t="n"/>
+      <c r="H93" s="3" t="n"/>
     </row>
     <row r="94">
       <c r="D94" s="2" t="n"/>
       <c r="F94" s="3" t="n"/>
+      <c r="H94" s="3" t="n"/>
     </row>
     <row r="95">
       <c r="D95" s="2" t="n"/>
       <c r="F95" s="3" t="n"/>
+      <c r="H95" s="3" t="n"/>
     </row>
     <row r="96">
       <c r="D96" s="2" t="n"/>
       <c r="F96" s="3" t="n"/>
+      <c r="H96" s="3" t="n"/>
     </row>
     <row r="97">
       <c r="D97" s="2" t="n"/>
       <c r="F97" s="3" t="n"/>
+      <c r="H97" s="3" t="n"/>
     </row>
     <row r="98">
       <c r="D98" s="2" t="n"/>
       <c r="F98" s="3" t="n"/>
+      <c r="H98" s="3" t="n"/>
     </row>
     <row r="99">
       <c r="D99" s="2" t="n"/>
       <c r="F99" s="3" t="n"/>
+      <c r="H99" s="3" t="n"/>
     </row>
     <row r="100">
       <c r="D100" s="2" t="n"/>
       <c r="F100" s="3" t="n"/>
+      <c r="H100" s="3" t="n"/>
     </row>
     <row r="101">
       <c r="D101" s="2" t="n"/>
       <c r="F101" s="3" t="n"/>
+      <c r="H101" s="3" t="n"/>
     </row>
     <row r="102">
       <c r="D102" s="2" t="n"/>
       <c r="F102" s="3" t="n"/>
+      <c r="H102" s="3" t="n"/>
     </row>
     <row r="103">
       <c r="D103" s="2" t="n"/>
       <c r="F103" s="3" t="n"/>
+      <c r="H103" s="3" t="n"/>
     </row>
     <row r="104">
       <c r="D104" s="2" t="n"/>
       <c r="F104" s="3" t="n"/>
+      <c r="H104" s="3" t="n"/>
     </row>
     <row r="105">
       <c r="D105" s="2" t="n"/>
       <c r="F105" s="3" t="n"/>
+      <c r="H105" s="3" t="n"/>
     </row>
     <row r="106">
       <c r="D106" s="2" t="n"/>
       <c r="F106" s="3" t="n"/>
+      <c r="H106" s="3" t="n"/>
     </row>
     <row r="107">
       <c r="D107" s="2" t="n"/>
       <c r="F107" s="3" t="n"/>
+      <c r="H107" s="3" t="n"/>
     </row>
     <row r="108">
       <c r="D108" s="2" t="n"/>
       <c r="F108" s="3" t="n"/>
+      <c r="H108" s="3" t="n"/>
     </row>
     <row r="109">
       <c r="D109" s="2" t="n"/>
       <c r="F109" s="3" t="n"/>
+      <c r="H109" s="3" t="n"/>
     </row>
     <row r="110">
       <c r="D110" s="2" t="n"/>
       <c r="F110" s="3" t="n"/>
+      <c r="H110" s="3" t="n"/>
     </row>
     <row r="111">
       <c r="D111" s="2" t="n"/>
       <c r="F111" s="3" t="n"/>
+      <c r="H111" s="3" t="n"/>
     </row>
     <row r="112">
       <c r="D112" s="2" t="n"/>
       <c r="F112" s="3" t="n"/>
+      <c r="H112" s="3" t="n"/>
     </row>
     <row r="113">
       <c r="D113" s="2" t="n"/>
       <c r="F113" s="3" t="n"/>
+      <c r="H113" s="3" t="n"/>
     </row>
     <row r="114">
       <c r="D114" s="2" t="n"/>
       <c r="F114" s="3" t="n"/>
+      <c r="H114" s="3" t="n"/>
     </row>
     <row r="115">
       <c r="D115" s="2" t="n"/>
       <c r="F115" s="3" t="n"/>
+      <c r="H115" s="3" t="n"/>
     </row>
     <row r="116">
       <c r="D116" s="2" t="n"/>
       <c r="F116" s="3" t="n"/>
+      <c r="H116" s="3" t="n"/>
     </row>
     <row r="117">
       <c r="D117" s="2" t="n"/>
       <c r="F117" s="3" t="n"/>
+      <c r="H117" s="3" t="n"/>
     </row>
     <row r="118">
       <c r="D118" s="2" t="n"/>
       <c r="F118" s="3" t="n"/>
+      <c r="H118" s="3" t="n"/>
     </row>
     <row r="119">
       <c r="D119" s="2" t="n"/>
       <c r="F119" s="3" t="n"/>
+      <c r="H119" s="3" t="n"/>
     </row>
     <row r="120">
       <c r="D120" s="2" t="n"/>
       <c r="F120" s="3" t="n"/>
+      <c r="H120" s="3" t="n"/>
     </row>
     <row r="121">
       <c r="D121" s="2" t="n"/>
       <c r="F121" s="3" t="n"/>
+      <c r="H121" s="3" t="n"/>
     </row>
     <row r="122">
       <c r="D122" s="2" t="n"/>
       <c r="F122" s="3" t="n"/>
+      <c r="H122" s="3" t="n"/>
     </row>
     <row r="123">
       <c r="D123" s="2" t="n"/>
       <c r="F123" s="3" t="n"/>
+      <c r="H123" s="3" t="n"/>
     </row>
     <row r="124">
       <c r="D124" s="2" t="n"/>
       <c r="F124" s="3" t="n"/>
+      <c r="H124" s="3" t="n"/>
     </row>
     <row r="125">
       <c r="D125" s="2" t="n"/>
       <c r="F125" s="3" t="n"/>
+      <c r="H125" s="3" t="n"/>
     </row>
     <row r="126">
       <c r="D126" s="2" t="n"/>
       <c r="F126" s="3" t="n"/>
+      <c r="H126" s="3" t="n"/>
     </row>
     <row r="127">
       <c r="D127" s="2" t="n"/>
       <c r="F127" s="3" t="n"/>
+      <c r="H127" s="3" t="n"/>
     </row>
     <row r="128">
       <c r="D128" s="2" t="n"/>
       <c r="F128" s="3" t="n"/>
+      <c r="H128" s="3" t="n"/>
     </row>
     <row r="129">
       <c r="D129" s="2" t="n"/>
       <c r="F129" s="3" t="n"/>
+      <c r="H129" s="3" t="n"/>
     </row>
     <row r="130">
       <c r="D130" s="2" t="n"/>
       <c r="F130" s="3" t="n"/>
+      <c r="H130" s="3" t="n"/>
     </row>
     <row r="131">
       <c r="D131" s="2" t="n"/>
       <c r="F131" s="3" t="n"/>
+      <c r="H131" s="3" t="n"/>
     </row>
     <row r="132">
       <c r="D132" s="2" t="n"/>
       <c r="F132" s="3" t="n"/>
+      <c r="H132" s="3" t="n"/>
     </row>
     <row r="133">
       <c r="D133" s="2" t="n"/>
       <c r="F133" s="3" t="n"/>
+      <c r="H133" s="3" t="n"/>
     </row>
     <row r="134">
       <c r="D134" s="2" t="n"/>
       <c r="F134" s="3" t="n"/>
+      <c r="H134" s="3" t="n"/>
     </row>
     <row r="135">
       <c r="D135" s="2" t="n"/>
       <c r="F135" s="3" t="n"/>
+      <c r="H135" s="3" t="n"/>
     </row>
     <row r="136">
       <c r="D136" s="2" t="n"/>
       <c r="F136" s="3" t="n"/>
+      <c r="H136" s="3" t="n"/>
     </row>
     <row r="137">
       <c r="D137" s="2" t="n"/>
       <c r="F137" s="3" t="n"/>
+      <c r="H137" s="3" t="n"/>
     </row>
     <row r="138">
       <c r="D138" s="2" t="n"/>
       <c r="F138" s="3" t="n"/>
+      <c r="H138" s="3" t="n"/>
     </row>
     <row r="139">
       <c r="D139" s="2" t="n"/>
       <c r="F139" s="3" t="n"/>
+      <c r="H139" s="3" t="n"/>
     </row>
     <row r="140">
       <c r="D140" s="2" t="n"/>
       <c r="F140" s="3" t="n"/>
+      <c r="H140" s="3" t="n"/>
     </row>
     <row r="141">
       <c r="D141" s="2" t="n"/>
       <c r="F141" s="3" t="n"/>
+      <c r="H141" s="3" t="n"/>
     </row>
     <row r="142">
       <c r="D142" s="2" t="n"/>
       <c r="F142" s="3" t="n"/>
+      <c r="H142" s="3" t="n"/>
     </row>
     <row r="143">
       <c r="D143" s="2" t="n"/>
       <c r="F143" s="3" t="n"/>
+      <c r="H143" s="3" t="n"/>
     </row>
     <row r="144">
       <c r="D144" s="2" t="n"/>
       <c r="F144" s="3" t="n"/>
+      <c r="H144" s="3" t="n"/>
     </row>
     <row r="145">
       <c r="D145" s="2" t="n"/>
       <c r="F145" s="3" t="n"/>
+      <c r="H145" s="3" t="n"/>
     </row>
     <row r="146">
       <c r="D146" s="2" t="n"/>
       <c r="F146" s="3" t="n"/>
+      <c r="H146" s="3" t="n"/>
     </row>
     <row r="147">
       <c r="D147" s="2" t="n"/>
       <c r="F147" s="3" t="n"/>
+      <c r="H147" s="3" t="n"/>
     </row>
     <row r="148">
       <c r="D148" s="2" t="n"/>
       <c r="F148" s="3" t="n"/>
+      <c r="H148" s="3" t="n"/>
     </row>
     <row r="149">
       <c r="D149" s="2" t="n"/>
       <c r="F149" s="3" t="n"/>
+      <c r="H149" s="3" t="n"/>
     </row>
     <row r="150">
       <c r="D150" s="2" t="n"/>
       <c r="F150" s="3" t="n"/>
+      <c r="H150" s="3" t="n"/>
     </row>
     <row r="151">
       <c r="D151" s="2" t="n"/>
       <c r="F151" s="3" t="n"/>
+      <c r="H151" s="3" t="n"/>
     </row>
     <row r="152">
       <c r="D152" s="2" t="n"/>
       <c r="F152" s="3" t="n"/>
+      <c r="H152" s="3" t="n"/>
     </row>
     <row r="153">
       <c r="D153" s="2" t="n"/>
       <c r="F153" s="3" t="n"/>
+      <c r="H153" s="3" t="n"/>
     </row>
     <row r="154">
       <c r="D154" s="2" t="n"/>
       <c r="F154" s="3" t="n"/>
+      <c r="H154" s="3" t="n"/>
     </row>
     <row r="155">
       <c r="D155" s="2" t="n"/>
       <c r="F155" s="3" t="n"/>
+      <c r="H155" s="3" t="n"/>
     </row>
     <row r="156">
       <c r="D156" s="2" t="n"/>
       <c r="F156" s="3" t="n"/>
+      <c r="H156" s="3" t="n"/>
     </row>
     <row r="157">
       <c r="D157" s="2" t="n"/>
       <c r="F157" s="3" t="n"/>
+      <c r="H157" s="3" t="n"/>
     </row>
     <row r="158">
       <c r="D158" s="2" t="n"/>
       <c r="F158" s="3" t="n"/>
+      <c r="H158" s="3" t="n"/>
     </row>
     <row r="159">
       <c r="D159" s="2" t="n"/>
       <c r="F159" s="3" t="n"/>
+      <c r="H159" s="3" t="n"/>
     </row>
     <row r="160">
       <c r="D160" s="2" t="n"/>
       <c r="F160" s="3" t="n"/>
+      <c r="H160" s="3" t="n"/>
     </row>
     <row r="161">
       <c r="D161" s="2" t="n"/>
       <c r="F161" s="3" t="n"/>
+      <c r="H161" s="3" t="n"/>
     </row>
     <row r="162">
       <c r="D162" s="2" t="n"/>
       <c r="F162" s="3" t="n"/>
+      <c r="H162" s="3" t="n"/>
     </row>
     <row r="163">
       <c r="D163" s="2" t="n"/>
       <c r="F163" s="3" t="n"/>
+      <c r="H163" s="3" t="n"/>
     </row>
     <row r="164">
       <c r="D164" s="2" t="n"/>
       <c r="F164" s="3" t="n"/>
+      <c r="H164" s="3" t="n"/>
     </row>
     <row r="165">
       <c r="D165" s="2" t="n"/>
       <c r="F165" s="3" t="n"/>
+      <c r="H165" s="3" t="n"/>
     </row>
     <row r="166">
       <c r="D166" s="2" t="n"/>
       <c r="F166" s="3" t="n"/>
+      <c r="H166" s="3" t="n"/>
     </row>
     <row r="167">
       <c r="D167" s="2" t="n"/>
       <c r="F167" s="3" t="n"/>
+      <c r="H167" s="3" t="n"/>
     </row>
     <row r="168">
       <c r="D168" s="2" t="n"/>
       <c r="F168" s="3" t="n"/>
+      <c r="H168" s="3" t="n"/>
     </row>
     <row r="169">
       <c r="D169" s="2" t="n"/>
       <c r="F169" s="3" t="n"/>
+      <c r="H169" s="3" t="n"/>
     </row>
     <row r="170">
       <c r="D170" s="2" t="n"/>
       <c r="F170" s="3" t="n"/>
+      <c r="H170" s="3" t="n"/>
     </row>
     <row r="171">
       <c r="D171" s="2" t="n"/>
       <c r="F171" s="3" t="n"/>
+      <c r="H171" s="3" t="n"/>
     </row>
     <row r="172">
       <c r="D172" s="2" t="n"/>
       <c r="F172" s="3" t="n"/>
+      <c r="H172" s="3" t="n"/>
     </row>
     <row r="173">
       <c r="D173" s="2" t="n"/>
       <c r="F173" s="3" t="n"/>
+      <c r="H173" s="3" t="n"/>
     </row>
     <row r="174">
       <c r="D174" s="2" t="n"/>
       <c r="F174" s="3" t="n"/>
+      <c r="H174" s="3" t="n"/>
     </row>
     <row r="175">
       <c r="D175" s="2" t="n"/>
       <c r="F175" s="3" t="n"/>
+      <c r="H175" s="3" t="n"/>
     </row>
     <row r="176">
       <c r="D176" s="2" t="n"/>
       <c r="F176" s="3" t="n"/>
+      <c r="H176" s="3" t="n"/>
     </row>
     <row r="177">
       <c r="D177" s="2" t="n"/>
       <c r="F177" s="3" t="n"/>
+      <c r="H177" s="3" t="n"/>
     </row>
     <row r="178">
       <c r="D178" s="2" t="n"/>
       <c r="F178" s="3" t="n"/>
+      <c r="H178" s="3" t="n"/>
     </row>
     <row r="179">
       <c r="D179" s="2" t="n"/>
       <c r="F179" s="3" t="n"/>
+      <c r="H179" s="3" t="n"/>
     </row>
     <row r="180">
       <c r="D180" s="2" t="n"/>
       <c r="F180" s="3" t="n"/>
+      <c r="H180" s="3" t="n"/>
     </row>
     <row r="181">
       <c r="D181" s="2" t="n"/>
       <c r="F181" s="3" t="n"/>
+      <c r="H181" s="3" t="n"/>
     </row>
     <row r="182">
       <c r="D182" s="2" t="n"/>
       <c r="F182" s="3" t="n"/>
+      <c r="H182" s="3" t="n"/>
     </row>
     <row r="183">
       <c r="D183" s="2" t="n"/>
       <c r="F183" s="3" t="n"/>
+      <c r="H183" s="3" t="n"/>
     </row>
     <row r="184">
       <c r="D184" s="2" t="n"/>
       <c r="F184" s="3" t="n"/>
+      <c r="H184" s="3" t="n"/>
     </row>
     <row r="185">
       <c r="D185" s="2" t="n"/>
       <c r="F185" s="3" t="n"/>
+      <c r="H185" s="3" t="n"/>
     </row>
     <row r="186">
       <c r="D186" s="2" t="n"/>
       <c r="F186" s="3" t="n"/>
+      <c r="H186" s="3" t="n"/>
     </row>
     <row r="187">
       <c r="D187" s="2" t="n"/>
       <c r="F187" s="3" t="n"/>
+      <c r="H187" s="3" t="n"/>
     </row>
     <row r="188">
       <c r="D188" s="2" t="n"/>
       <c r="F188" s="3" t="n"/>
+      <c r="H188" s="3" t="n"/>
     </row>
     <row r="189">
       <c r="D189" s="2" t="n"/>
       <c r="F189" s="3" t="n"/>
+      <c r="H189" s="3" t="n"/>
     </row>
     <row r="190">
       <c r="D190" s="2" t="n"/>
       <c r="F190" s="3" t="n"/>
+      <c r="H190" s="3" t="n"/>
     </row>
     <row r="191">
       <c r="D191" s="2" t="n"/>
       <c r="F191" s="3" t="n"/>
+      <c r="H191" s="3" t="n"/>
     </row>
     <row r="192">
       <c r="D192" s="2" t="n"/>
       <c r="F192" s="3" t="n"/>
+      <c r="H192" s="3" t="n"/>
     </row>
     <row r="193">
       <c r="D193" s="2" t="n"/>
       <c r="F193" s="3" t="n"/>
+      <c r="H193" s="3" t="n"/>
     </row>
     <row r="194">
       <c r="D194" s="2" t="n"/>
       <c r="F194" s="3" t="n"/>
+      <c r="H194" s="3" t="n"/>
     </row>
     <row r="195">
       <c r="D195" s="2" t="n"/>
       <c r="F195" s="3" t="n"/>
+      <c r="H195" s="3" t="n"/>
     </row>
     <row r="196">
       <c r="D196" s="2" t="n"/>
       <c r="F196" s="3" t="n"/>
+      <c r="H196" s="3" t="n"/>
     </row>
     <row r="197">
       <c r="D197" s="2" t="n"/>
       <c r="F197" s="3" t="n"/>
+      <c r="H197" s="3" t="n"/>
     </row>
     <row r="198">
       <c r="D198" s="2" t="n"/>
       <c r="F198" s="3" t="n"/>
+      <c r="H198" s="3" t="n"/>
     </row>
     <row r="199">
       <c r="D199" s="2" t="n"/>
       <c r="F199" s="3" t="n"/>
+      <c r="H199" s="3" t="n"/>
     </row>
     <row r="200">
       <c r="D200" s="2" t="n"/>
       <c r="F200" s="3" t="n"/>
+      <c r="H200" s="3" t="n"/>
     </row>
     <row r="201">
       <c r="D201" s="2" t="n"/>
       <c r="F201" s="3" t="n"/>
+      <c r="H201" s="3" t="n"/>
     </row>
     <row r="202">
       <c r="D202" s="2" t="n"/>
       <c r="F202" s="3" t="n"/>
+      <c r="H202" s="3" t="n"/>
     </row>
     <row r="203">
       <c r="D203" s="2" t="n"/>
       <c r="F203" s="3" t="n"/>
+      <c r="H203" s="3" t="n"/>
     </row>
     <row r="204">
       <c r="D204" s="2" t="n"/>
       <c r="F204" s="3" t="n"/>
+      <c r="H204" s="3" t="n"/>
     </row>
     <row r="205">
       <c r="D205" s="2" t="n"/>
       <c r="F205" s="3" t="n"/>
+      <c r="H205" s="3" t="n"/>
     </row>
     <row r="206">
       <c r="D206" s="2" t="n"/>
       <c r="F206" s="3" t="n"/>
+      <c r="H206" s="3" t="n"/>
     </row>
     <row r="207">
       <c r="D207" s="2" t="n"/>
       <c r="F207" s="3" t="n"/>
+      <c r="H207" s="3" t="n"/>
     </row>
     <row r="208">
       <c r="D208" s="2" t="n"/>
       <c r="F208" s="3" t="n"/>
+      <c r="H208" s="3" t="n"/>
     </row>
     <row r="209">
       <c r="D209" s="2" t="n"/>
       <c r="F209" s="3" t="n"/>
+      <c r="H209" s="3" t="n"/>
     </row>
     <row r="210">
       <c r="D210" s="2" t="n"/>
       <c r="F210" s="3" t="n"/>
+      <c r="H210" s="3" t="n"/>
     </row>
     <row r="211">
       <c r="D211" s="2" t="n"/>
       <c r="F211" s="3" t="n"/>
+      <c r="H211" s="3" t="n"/>
     </row>
     <row r="212">
       <c r="D212" s="2" t="n"/>
       <c r="F212" s="3" t="n"/>
+      <c r="H212" s="3" t="n"/>
     </row>
     <row r="213">
       <c r="D213" s="2" t="n"/>
       <c r="F213" s="3" t="n"/>
+      <c r="H213" s="3" t="n"/>
     </row>
     <row r="214">
       <c r="D214" s="2" t="n"/>
       <c r="F214" s="3" t="n"/>
+      <c r="H214" s="3" t="n"/>
     </row>
     <row r="215">
       <c r="D215" s="2" t="n"/>
       <c r="F215" s="3" t="n"/>
+      <c r="H215" s="3" t="n"/>
     </row>
     <row r="216">
       <c r="D216" s="2" t="n"/>
       <c r="F216" s="3" t="n"/>
+      <c r="H216" s="3" t="n"/>
     </row>
     <row r="217">
       <c r="D217" s="2" t="n"/>
       <c r="F217" s="3" t="n"/>
+      <c r="H217" s="3" t="n"/>
     </row>
     <row r="218">
       <c r="D218" s="2" t="n"/>
       <c r="F218" s="3" t="n"/>
+      <c r="H218" s="3" t="n"/>
     </row>
     <row r="219">
       <c r="D219" s="2" t="n"/>
       <c r="F219" s="3" t="n"/>
+      <c r="H219" s="3" t="n"/>
     </row>
     <row r="220">
       <c r="D220" s="2" t="n"/>
       <c r="F220" s="3" t="n"/>
+      <c r="H220" s="3" t="n"/>
     </row>
     <row r="221">
       <c r="D221" s="2" t="n"/>
       <c r="F221" s="3" t="n"/>
+      <c r="H221" s="3" t="n"/>
     </row>
     <row r="222">
       <c r="D222" s="2" t="n"/>
       <c r="F222" s="3" t="n"/>
+      <c r="H222" s="3" t="n"/>
     </row>
     <row r="223">
       <c r="D223" s="2" t="n"/>
       <c r="F223" s="3" t="n"/>
+      <c r="H223" s="3" t="n"/>
     </row>
     <row r="224">
       <c r="D224" s="2" t="n"/>
       <c r="F224" s="3" t="n"/>
+      <c r="H224" s="3" t="n"/>
     </row>
     <row r="225">
       <c r="D225" s="2" t="n"/>
       <c r="F225" s="3" t="n"/>
+      <c r="H225" s="3" t="n"/>
     </row>
     <row r="226">
       <c r="D226" s="2" t="n"/>
       <c r="F226" s="3" t="n"/>
+      <c r="H226" s="3" t="n"/>
     </row>
     <row r="227">
       <c r="D227" s="2" t="n"/>
       <c r="F227" s="3" t="n"/>
+      <c r="H227" s="3" t="n"/>
     </row>
     <row r="228">
       <c r="D228" s="2" t="n"/>
       <c r="F228" s="3" t="n"/>
+      <c r="H228" s="3" t="n"/>
     </row>
     <row r="229">
       <c r="D229" s="2" t="n"/>
       <c r="F229" s="3" t="n"/>
+      <c r="H229" s="3" t="n"/>
     </row>
     <row r="230">
       <c r="D230" s="2" t="n"/>
       <c r="F230" s="3" t="n"/>
+      <c r="H230" s="3" t="n"/>
     </row>
     <row r="231">
       <c r="D231" s="2" t="n"/>
       <c r="F231" s="3" t="n"/>
+      <c r="H231" s="3" t="n"/>
     </row>
     <row r="232">
       <c r="D232" s="2" t="n"/>
       <c r="F232" s="3" t="n"/>
+      <c r="H232" s="3" t="n"/>
     </row>
     <row r="233">
       <c r="D233" s="2" t="n"/>
       <c r="F233" s="3" t="n"/>
+      <c r="H233" s="3" t="n"/>
     </row>
     <row r="234">
       <c r="D234" s="2" t="n"/>
       <c r="F234" s="3" t="n"/>
+      <c r="H234" s="3" t="n"/>
     </row>
     <row r="235">
       <c r="D235" s="2" t="n"/>
       <c r="F235" s="3" t="n"/>
+      <c r="H235" s="3" t="n"/>
     </row>
     <row r="236">
       <c r="D236" s="2" t="n"/>
       <c r="F236" s="3" t="n"/>
+      <c r="H236" s="3" t="n"/>
     </row>
     <row r="237">
       <c r="D237" s="2" t="n"/>
       <c r="F237" s="3" t="n"/>
+      <c r="H237" s="3" t="n"/>
     </row>
     <row r="238">
       <c r="D238" s="2" t="n"/>
       <c r="F238" s="3" t="n"/>
+      <c r="H238" s="3" t="n"/>
     </row>
     <row r="239">
       <c r="D239" s="2" t="n"/>
       <c r="F239" s="3" t="n"/>
+      <c r="H239" s="3" t="n"/>
     </row>
     <row r="240">
       <c r="D240" s="2" t="n"/>
       <c r="F240" s="3" t="n"/>
+      <c r="H240" s="3" t="n"/>
     </row>
     <row r="241">
       <c r="D241" s="2" t="n"/>
       <c r="F241" s="3" t="n"/>
+      <c r="H241" s="3" t="n"/>
     </row>
     <row r="242">
       <c r="D242" s="2" t="n"/>
       <c r="F242" s="3" t="n"/>
+      <c r="H242" s="3" t="n"/>
     </row>
     <row r="243">
       <c r="D243" s="2" t="n"/>
       <c r="F243" s="3" t="n"/>
+      <c r="H243" s="3" t="n"/>
     </row>
     <row r="244">
       <c r="D244" s="2" t="n"/>
       <c r="F244" s="3" t="n"/>
+      <c r="H244" s="3" t="n"/>
     </row>
     <row r="245">
       <c r="D245" s="2" t="n"/>
       <c r="F245" s="3" t="n"/>
+      <c r="H245" s="3" t="n"/>
     </row>
     <row r="246">
       <c r="D246" s="2" t="n"/>
       <c r="F246" s="3" t="n"/>
+      <c r="H246" s="3" t="n"/>
     </row>
     <row r="247">
       <c r="D247" s="2" t="n"/>
       <c r="F247" s="3" t="n"/>
+      <c r="H247" s="3" t="n"/>
     </row>
     <row r="248">
       <c r="D248" s="2" t="n"/>
       <c r="F248" s="3" t="n"/>
+      <c r="H248" s="3" t="n"/>
     </row>
     <row r="249">
       <c r="D249" s="2" t="n"/>
       <c r="F249" s="3" t="n"/>
+      <c r="H249" s="3" t="n"/>
     </row>
     <row r="250">
       <c r="D250" s="2" t="n"/>
       <c r="F250" s="3" t="n"/>
+      <c r="H250" s="3" t="n"/>
     </row>
     <row r="251">
       <c r="D251" s="2" t="n"/>
       <c r="F251" s="3" t="n"/>
+      <c r="H251" s="3" t="n"/>
     </row>
     <row r="252">
       <c r="D252" s="2" t="n"/>
       <c r="F252" s="3" t="n"/>
+      <c r="H252" s="3" t="n"/>
     </row>
     <row r="253">
       <c r="D253" s="2" t="n"/>
       <c r="F253" s="3" t="n"/>
+      <c r="H253" s="3" t="n"/>
     </row>
     <row r="254">
       <c r="D254" s="2" t="n"/>
       <c r="F254" s="3" t="n"/>
+      <c r="H254" s="3" t="n"/>
     </row>
     <row r="255">
       <c r="D255" s="2" t="n"/>
       <c r="F255" s="3" t="n"/>
+      <c r="H255" s="3" t="n"/>
     </row>
     <row r="256">
       <c r="D256" s="2" t="n"/>
       <c r="F256" s="3" t="n"/>
+      <c r="H256" s="3" t="n"/>
     </row>
     <row r="257">
       <c r="D257" s="2" t="n"/>
       <c r="F257" s="3" t="n"/>
+      <c r="H257" s="3" t="n"/>
     </row>
     <row r="258">
       <c r="D258" s="2" t="n"/>
       <c r="F258" s="3" t="n"/>
+      <c r="H258" s="3" t="n"/>
     </row>
     <row r="259">
       <c r="D259" s="2" t="n"/>
       <c r="F259" s="3" t="n"/>
+      <c r="H259" s="3" t="n"/>
     </row>
     <row r="260">
       <c r="D260" s="2" t="n"/>
       <c r="F260" s="3" t="n"/>
+      <c r="H260" s="3" t="n"/>
     </row>
     <row r="261">
       <c r="D261" s="2" t="n"/>
       <c r="F261" s="3" t="n"/>
+      <c r="H261" s="3" t="n"/>
     </row>
     <row r="262">
       <c r="D262" s="2" t="n"/>
       <c r="F262" s="3" t="n"/>
+      <c r="H262" s="3" t="n"/>
     </row>
     <row r="263">
       <c r="D263" s="2" t="n"/>
       <c r="F263" s="3" t="n"/>
+      <c r="H263" s="3" t="n"/>
     </row>
     <row r="264">
       <c r="D264" s="2" t="n"/>
       <c r="F264" s="3" t="n"/>
+      <c r="H264" s="3" t="n"/>
     </row>
     <row r="265">
       <c r="D265" s="2" t="n"/>
       <c r="F265" s="3" t="n"/>
+      <c r="H265" s="3" t="n"/>
     </row>
     <row r="266">
       <c r="D266" s="2" t="n"/>
       <c r="F266" s="3" t="n"/>
+      <c r="H266" s="3" t="n"/>
     </row>
     <row r="267">
       <c r="D267" s="2" t="n"/>
       <c r="F267" s="3" t="n"/>
+      <c r="H267" s="3" t="n"/>
     </row>
     <row r="268">
       <c r="D268" s="2" t="n"/>
       <c r="F268" s="3" t="n"/>
+      <c r="H268" s="3" t="n"/>
     </row>
     <row r="269">
       <c r="D269" s="2" t="n"/>
       <c r="F269" s="3" t="n"/>
+      <c r="H269" s="3" t="n"/>
     </row>
     <row r="270">
       <c r="D270" s="2" t="n"/>
       <c r="F270" s="3" t="n"/>
+      <c r="H270" s="3" t="n"/>
     </row>
     <row r="271">
       <c r="D271" s="2" t="n"/>
       <c r="F271" s="3" t="n"/>
+      <c r="H271" s="3" t="n"/>
     </row>
     <row r="272">
       <c r="D272" s="2" t="n"/>
       <c r="F272" s="3" t="n"/>
+      <c r="H272" s="3" t="n"/>
     </row>
     <row r="273">
       <c r="D273" s="2" t="n"/>
       <c r="F273" s="3" t="n"/>
+      <c r="H273" s="3" t="n"/>
     </row>
     <row r="274">
       <c r="D274" s="2" t="n"/>
       <c r="F274" s="3" t="n"/>
+      <c r="H274" s="3" t="n"/>
     </row>
     <row r="275">
       <c r="D275" s="2" t="n"/>
       <c r="F275" s="3" t="n"/>
+      <c r="H275" s="3" t="n"/>
     </row>
     <row r="276">
       <c r="D276" s="2" t="n"/>
       <c r="F276" s="3" t="n"/>
+      <c r="H276" s="3" t="n"/>
     </row>
     <row r="277">
       <c r="D277" s="2" t="n"/>
       <c r="F277" s="3" t="n"/>
+      <c r="H277" s="3" t="n"/>
     </row>
     <row r="278">
       <c r="D278" s="2" t="n"/>
       <c r="F278" s="3" t="n"/>
+      <c r="H278" s="3" t="n"/>
     </row>
     <row r="279">
       <c r="D279" s="2" t="n"/>
       <c r="F279" s="3" t="n"/>
+      <c r="H279" s="3" t="n"/>
     </row>
     <row r="280">
       <c r="D280" s="2" t="n"/>
       <c r="F280" s="3" t="n"/>
+      <c r="H280" s="3" t="n"/>
     </row>
     <row r="281">
       <c r="D281" s="2" t="n"/>
       <c r="F281" s="3" t="n"/>
+      <c r="H281" s="3" t="n"/>
     </row>
     <row r="282">
       <c r="D282" s="2" t="n"/>
       <c r="F282" s="3" t="n"/>
+      <c r="H282" s="3" t="n"/>
     </row>
     <row r="283">
       <c r="D283" s="2" t="n"/>
       <c r="F283" s="3" t="n"/>
+      <c r="H283" s="3" t="n"/>
     </row>
     <row r="284">
       <c r="D284" s="2" t="n"/>
       <c r="F284" s="3" t="n"/>
+      <c r="H284" s="3" t="n"/>
     </row>
     <row r="285">
       <c r="D285" s="2" t="n"/>
       <c r="F285" s="3" t="n"/>
+      <c r="H285" s="3" t="n"/>
     </row>
     <row r="286">
       <c r="D286" s="2" t="n"/>
       <c r="F286" s="3" t="n"/>
+      <c r="H286" s="3" t="n"/>
     </row>
     <row r="287">
       <c r="D287" s="2" t="n"/>
       <c r="F287" s="3" t="n"/>
+      <c r="H287" s="3" t="n"/>
     </row>
     <row r="288">
       <c r="D288" s="2" t="n"/>
       <c r="F288" s="3" t="n"/>
+      <c r="H288" s="3" t="n"/>
     </row>
     <row r="289">
       <c r="D289" s="2" t="n"/>
       <c r="F289" s="3" t="n"/>
+      <c r="H289" s="3" t="n"/>
     </row>
     <row r="290">
       <c r="D290" s="2" t="n"/>
       <c r="F290" s="3" t="n"/>
+      <c r="H290" s="3" t="n"/>
     </row>
     <row r="291">
       <c r="D291" s="2" t="n"/>
       <c r="F291" s="3" t="n"/>
+      <c r="H291" s="3" t="n"/>
     </row>
     <row r="292">
       <c r="D292" s="2" t="n"/>
       <c r="F292" s="3" t="n"/>
+      <c r="H292" s="3" t="n"/>
     </row>
     <row r="293">
       <c r="D293" s="2" t="n"/>
       <c r="F293" s="3" t="n"/>
+      <c r="H293" s="3" t="n"/>
     </row>
     <row r="294">
       <c r="D294" s="2" t="n"/>
       <c r="F294" s="3" t="n"/>
+      <c r="H294" s="3" t="n"/>
     </row>
     <row r="295">
       <c r="D295" s="2" t="n"/>
       <c r="F295" s="3" t="n"/>
+      <c r="H295" s="3" t="n"/>
     </row>
     <row r="296">
       <c r="D296" s="2" t="n"/>
       <c r="F296" s="3" t="n"/>
+      <c r="H296" s="3" t="n"/>
     </row>
     <row r="297">
       <c r="D297" s="2" t="n"/>
       <c r="F297" s="3" t="n"/>
+      <c r="H297" s="3" t="n"/>
     </row>
     <row r="298">
       <c r="D298" s="2" t="n"/>
       <c r="F298" s="3" t="n"/>
+      <c r="H298" s="3" t="n"/>
     </row>
     <row r="299">
       <c r="D299" s="2" t="n"/>
       <c r="F299" s="3" t="n"/>
+      <c r="H299" s="3" t="n"/>
     </row>
     <row r="300">
       <c r="D300" s="2" t="n"/>
       <c r="F300" s="3" t="n"/>
+      <c r="H300" s="3" t="n"/>
     </row>
     <row r="301">
       <c r="D301" s="2" t="n"/>
       <c r="F301" s="3" t="n"/>
+      <c r="H301" s="3" t="n"/>
     </row>
     <row r="302">
       <c r="D302" s="2" t="n"/>
       <c r="F302" s="3" t="n"/>
+      <c r="H302" s="3" t="n"/>
     </row>
     <row r="303">
       <c r="D303" s="2" t="n"/>
       <c r="F303" s="3" t="n"/>
+      <c r="H303" s="3" t="n"/>
     </row>
     <row r="304">
       <c r="D304" s="2" t="n"/>
       <c r="F304" s="3" t="n"/>
+      <c r="H304" s="3" t="n"/>
     </row>
     <row r="305">
       <c r="D305" s="2" t="n"/>
       <c r="F305" s="3" t="n"/>
+      <c r="H305" s="3" t="n"/>
     </row>
     <row r="306">
       <c r="D306" s="2" t="n"/>
       <c r="F306" s="3" t="n"/>
+      <c r="H306" s="3" t="n"/>
     </row>
     <row r="307">
       <c r="D307" s="2" t="n"/>
       <c r="F307" s="3" t="n"/>
+      <c r="H307" s="3" t="n"/>
     </row>
     <row r="308">
       <c r="D308" s="2" t="n"/>
       <c r="F308" s="3" t="n"/>
+      <c r="H308" s="3" t="n"/>
     </row>
     <row r="309">
       <c r="D309" s="2" t="n"/>
       <c r="F309" s="3" t="n"/>
+      <c r="H309" s="3" t="n"/>
     </row>
     <row r="310">
       <c r="D310" s="2" t="n"/>
       <c r="F310" s="3" t="n"/>
+      <c r="H310" s="3" t="n"/>
     </row>
     <row r="311">
       <c r="D311" s="2" t="n"/>
       <c r="F311" s="3" t="n"/>
+      <c r="H311" s="3" t="n"/>
     </row>
     <row r="312">
       <c r="D312" s="2" t="n"/>
       <c r="F312" s="3" t="n"/>
+      <c r="H312" s="3" t="n"/>
     </row>
     <row r="313">
       <c r="D313" s="2" t="n"/>
       <c r="F313" s="3" t="n"/>
+      <c r="H313" s="3" t="n"/>
     </row>
     <row r="314">
       <c r="D314" s="2" t="n"/>
       <c r="F314" s="3" t="n"/>
+      <c r="H314" s="3" t="n"/>
     </row>
     <row r="315">
       <c r="D315" s="2" t="n"/>
       <c r="F315" s="3" t="n"/>
+      <c r="H315" s="3" t="n"/>
     </row>
     <row r="316">
       <c r="D316" s="2" t="n"/>
       <c r="F316" s="3" t="n"/>
+      <c r="H316" s="3" t="n"/>
     </row>
     <row r="317">
       <c r="D317" s="2" t="n"/>
       <c r="F317" s="3" t="n"/>
+      <c r="H317" s="3" t="n"/>
     </row>
     <row r="318">
       <c r="D318" s="2" t="n"/>
       <c r="F318" s="3" t="n"/>
+      <c r="H318" s="3" t="n"/>
     </row>
     <row r="319">
       <c r="D319" s="2" t="n"/>
       <c r="F319" s="3" t="n"/>
+      <c r="H319" s="3" t="n"/>
     </row>
     <row r="320">
       <c r="D320" s="2" t="n"/>
       <c r="F320" s="3" t="n"/>
+      <c r="H320" s="3" t="n"/>
     </row>
     <row r="321">
       <c r="D321" s="2" t="n"/>
       <c r="F321" s="3" t="n"/>
+      <c r="H321" s="3" t="n"/>
     </row>
     <row r="322">
       <c r="D322" s="2" t="n"/>
       <c r="F322" s="3" t="n"/>
+      <c r="H322" s="3" t="n"/>
     </row>
     <row r="323">
       <c r="D323" s="2" t="n"/>
       <c r="F323" s="3" t="n"/>
+      <c r="H323" s="3" t="n"/>
     </row>
     <row r="324">
       <c r="D324" s="2" t="n"/>
       <c r="F324" s="3" t="n"/>
+      <c r="H324" s="3" t="n"/>
     </row>
     <row r="325">
       <c r="D325" s="2" t="n"/>
       <c r="F325" s="3" t="n"/>
+      <c r="H325" s="3" t="n"/>
     </row>
     <row r="326">
       <c r="D326" s="2" t="n"/>
       <c r="F326" s="3" t="n"/>
+      <c r="H326" s="3" t="n"/>
     </row>
     <row r="327">
       <c r="D327" s="2" t="n"/>
       <c r="F327" s="3" t="n"/>
+      <c r="H327" s="3" t="n"/>
     </row>
     <row r="328">
       <c r="D328" s="2" t="n"/>
       <c r="F328" s="3" t="n"/>
+      <c r="H328" s="3" t="n"/>
     </row>
     <row r="329">
       <c r="D329" s="2" t="n"/>
       <c r="F329" s="3" t="n"/>
+      <c r="H329" s="3" t="n"/>
     </row>
     <row r="330">
       <c r="D330" s="2" t="n"/>
       <c r="F330" s="3" t="n"/>
+      <c r="H330" s="3" t="n"/>
     </row>
     <row r="331">
       <c r="D331" s="2" t="n"/>
       <c r="F331" s="3" t="n"/>
+      <c r="H331" s="3" t="n"/>
     </row>
     <row r="332">
       <c r="D332" s="2" t="n"/>
       <c r="F332" s="3" t="n"/>
+      <c r="H332" s="3" t="n"/>
     </row>
     <row r="333">
       <c r="D333" s="2" t="n"/>
       <c r="F333" s="3" t="n"/>
+      <c r="H333" s="3" t="n"/>
     </row>
     <row r="334">
       <c r="D334" s="2" t="n"/>
       <c r="F334" s="3" t="n"/>
+      <c r="H334" s="3" t="n"/>
     </row>
     <row r="335">
       <c r="D335" s="2" t="n"/>
       <c r="F335" s="3" t="n"/>
+      <c r="H335" s="3" t="n"/>
     </row>
     <row r="336">
       <c r="D336" s="2" t="n"/>
       <c r="F336" s="3" t="n"/>
+      <c r="H336" s="3" t="n"/>
     </row>
     <row r="337">
       <c r="D337" s="2" t="n"/>
       <c r="F337" s="3" t="n"/>
+      <c r="H337" s="3" t="n"/>
     </row>
     <row r="338">
       <c r="D338" s="2" t="n"/>
       <c r="F338" s="3" t="n"/>
+      <c r="H338" s="3" t="n"/>
     </row>
     <row r="339">
       <c r="D339" s="2" t="n"/>
       <c r="F339" s="3" t="n"/>
+      <c r="H339" s="3" t="n"/>
     </row>
     <row r="340">
       <c r="D340" s="2" t="n"/>
       <c r="F340" s="3" t="n"/>
+      <c r="H340" s="3" t="n"/>
     </row>
     <row r="341">
       <c r="D341" s="2" t="n"/>
       <c r="F341" s="3" t="n"/>
+      <c r="H341" s="3" t="n"/>
     </row>
     <row r="342">
       <c r="D342" s="2" t="n"/>
       <c r="F342" s="3" t="n"/>
+      <c r="H342" s="3" t="n"/>
     </row>
     <row r="343">
       <c r="D343" s="2" t="n"/>
       <c r="F343" s="3" t="n"/>
+      <c r="H343" s="3" t="n"/>
     </row>
     <row r="344">
       <c r="D344" s="2" t="n"/>
       <c r="F344" s="3" t="n"/>
+      <c r="H344" s="3" t="n"/>
     </row>
     <row r="345">
       <c r="D345" s="2" t="n"/>
       <c r="F345" s="3" t="n"/>
+      <c r="H345" s="3" t="n"/>
     </row>
     <row r="346">
       <c r="D346" s="2" t="n"/>
       <c r="F346" s="3" t="n"/>
+      <c r="H346" s="3" t="n"/>
     </row>
     <row r="347">
       <c r="D347" s="2" t="n"/>
       <c r="F347" s="3" t="n"/>
+      <c r="H347" s="3" t="n"/>
     </row>
     <row r="348">
       <c r="D348" s="2" t="n"/>
       <c r="F348" s="3" t="n"/>
+      <c r="H348" s="3" t="n"/>
     </row>
     <row r="349">
       <c r="D349" s="2" t="n"/>
       <c r="F349" s="3" t="n"/>
+      <c r="H349" s="3" t="n"/>
     </row>
     <row r="350">
       <c r="D350" s="2" t="n"/>
       <c r="F350" s="3" t="n"/>
+      <c r="H350" s="3" t="n"/>
     </row>
     <row r="351">
       <c r="D351" s="2" t="n"/>
       <c r="F351" s="3" t="n"/>
+      <c r="H351" s="3" t="n"/>
     </row>
     <row r="352">
       <c r="D352" s="2" t="n"/>
       <c r="F352" s="3" t="n"/>
+      <c r="H352" s="3" t="n"/>
     </row>
     <row r="353">
       <c r="D353" s="2" t="n"/>
       <c r="F353" s="3" t="n"/>
+      <c r="H353" s="3" t="n"/>
     </row>
     <row r="354">
       <c r="D354" s="2" t="n"/>
       <c r="F354" s="3" t="n"/>
+      <c r="H354" s="3" t="n"/>
     </row>
     <row r="355">
       <c r="D355" s="2" t="n"/>
       <c r="F355" s="3" t="n"/>
+      <c r="H355" s="3" t="n"/>
     </row>
     <row r="356">
       <c r="D356" s="2" t="n"/>
       <c r="F356" s="3" t="n"/>
+      <c r="H356" s="3" t="n"/>
     </row>
     <row r="357">
       <c r="D357" s="2" t="n"/>
       <c r="F357" s="3" t="n"/>
+      <c r="H357" s="3" t="n"/>
     </row>
     <row r="358">
       <c r="D358" s="2" t="n"/>
       <c r="F358" s="3" t="n"/>
+      <c r="H358" s="3" t="n"/>
     </row>
     <row r="359">
       <c r="D359" s="2" t="n"/>
       <c r="F359" s="3" t="n"/>
+      <c r="H359" s="3" t="n"/>
     </row>
     <row r="360">
       <c r="D360" s="2" t="n"/>
       <c r="F360" s="3" t="n"/>
+      <c r="H360" s="3" t="n"/>
     </row>
     <row r="361">
       <c r="D361" s="2" t="n"/>
       <c r="F361" s="3" t="n"/>
+      <c r="H361" s="3" t="n"/>
     </row>
     <row r="362">
       <c r="D362" s="2" t="n"/>
       <c r="F362" s="3" t="n"/>
+      <c r="H362" s="3" t="n"/>
     </row>
     <row r="363">
       <c r="D363" s="2" t="n"/>
       <c r="F363" s="3" t="n"/>
+      <c r="H363" s="3" t="n"/>
     </row>
     <row r="364">
       <c r="D364" s="2" t="n"/>
       <c r="F364" s="3" t="n"/>
+      <c r="H364" s="3" t="n"/>
     </row>
     <row r="365">
       <c r="D365" s="2" t="n"/>
       <c r="F365" s="3" t="n"/>
+      <c r="H365" s="3" t="n"/>
     </row>
     <row r="366">
       <c r="D366" s="2" t="n"/>
       <c r="F366" s="3" t="n"/>
+      <c r="H366" s="3" t="n"/>
     </row>
     <row r="367">
       <c r="D367" s="2" t="n"/>
       <c r="F367" s="3" t="n"/>
+      <c r="H367" s="3" t="n"/>
     </row>
     <row r="368">
       <c r="D368" s="2" t="n"/>
       <c r="F368" s="3" t="n"/>
+      <c r="H368" s="3" t="n"/>
     </row>
     <row r="369">
       <c r="D369" s="2" t="n"/>
       <c r="F369" s="3" t="n"/>
+      <c r="H369" s="3" t="n"/>
     </row>
     <row r="370">
       <c r="D370" s="2" t="n"/>
       <c r="F370" s="3" t="n"/>
+      <c r="H370" s="3" t="n"/>
     </row>
     <row r="371">
       <c r="D371" s="2" t="n"/>
       <c r="F371" s="3" t="n"/>
+      <c r="H371" s="3" t="n"/>
     </row>
     <row r="372">
       <c r="D372" s="2" t="n"/>
       <c r="F372" s="3" t="n"/>
+      <c r="H372" s="3" t="n"/>
     </row>
     <row r="373">
       <c r="D373" s="2" t="n"/>
       <c r="F373" s="3" t="n"/>
+      <c r="H373" s="3" t="n"/>
     </row>
     <row r="374">
       <c r="D374" s="2" t="n"/>
       <c r="F374" s="3" t="n"/>
+      <c r="H374" s="3" t="n"/>
     </row>
     <row r="375">
       <c r="D375" s="2" t="n"/>
       <c r="F375" s="3" t="n"/>
+      <c r="H375" s="3" t="n"/>
     </row>
     <row r="376">
       <c r="D376" s="2" t="n"/>
       <c r="F376" s="3" t="n"/>
+      <c r="H376" s="3" t="n"/>
     </row>
     <row r="377">
       <c r="D377" s="2" t="n"/>
       <c r="F377" s="3" t="n"/>
+      <c r="H377" s="3" t="n"/>
     </row>
     <row r="378">
       <c r="D378" s="2" t="n"/>
       <c r="F378" s="3" t="n"/>
+      <c r="H378" s="3" t="n"/>
     </row>
     <row r="379">
       <c r="D379" s="2" t="n"/>
       <c r="F379" s="3" t="n"/>
+      <c r="H379" s="3" t="n"/>
     </row>
     <row r="380">
       <c r="D380" s="2" t="n"/>
       <c r="F380" s="3" t="n"/>
+      <c r="H380" s="3" t="n"/>
     </row>
     <row r="381">
       <c r="D381" s="2" t="n"/>
       <c r="F381" s="3" t="n"/>
+      <c r="H381" s="3" t="n"/>
     </row>
     <row r="382">
       <c r="D382" s="2" t="n"/>
       <c r="F382" s="3" t="n"/>
+      <c r="H382" s="3" t="n"/>
     </row>
     <row r="383">
       <c r="D383" s="2" t="n"/>
       <c r="F383" s="3" t="n"/>
+      <c r="H383" s="3" t="n"/>
     </row>
     <row r="384">
       <c r="D384" s="2" t="n"/>
       <c r="F384" s="3" t="n"/>
+      <c r="H384" s="3" t="n"/>
     </row>
     <row r="385">
       <c r="D385" s="2" t="n"/>
       <c r="F385" s="3" t="n"/>
+      <c r="H385" s="3" t="n"/>
     </row>
     <row r="386">
       <c r="D386" s="2" t="n"/>
       <c r="F386" s="3" t="n"/>
+      <c r="H386" s="3" t="n"/>
     </row>
     <row r="387">
       <c r="D387" s="2" t="n"/>
       <c r="F387" s="3" t="n"/>
+      <c r="H387" s="3" t="n"/>
     </row>
     <row r="388">
       <c r="D388" s="2" t="n"/>
       <c r="F388" s="3" t="n"/>
+      <c r="H388" s="3" t="n"/>
     </row>
     <row r="389">
       <c r="D389" s="2" t="n"/>
       <c r="F389" s="3" t="n"/>
+      <c r="H389" s="3" t="n"/>
     </row>
     <row r="390">
       <c r="D390" s="2" t="n"/>
       <c r="F390" s="3" t="n"/>
+      <c r="H390" s="3" t="n"/>
     </row>
     <row r="391">
       <c r="D391" s="2" t="n"/>
       <c r="F391" s="3" t="n"/>
+      <c r="H391" s="3" t="n"/>
     </row>
     <row r="392">
       <c r="D392" s="2" t="n"/>
       <c r="F392" s="3" t="n"/>
+      <c r="H392" s="3" t="n"/>
     </row>
     <row r="393">
       <c r="D393" s="2" t="n"/>
       <c r="F393" s="3" t="n"/>
+      <c r="H393" s="3" t="n"/>
     </row>
     <row r="394">
       <c r="D394" s="2" t="n"/>
       <c r="F394" s="3" t="n"/>
+      <c r="H394" s="3" t="n"/>
     </row>
     <row r="395">
       <c r="D395" s="2" t="n"/>
       <c r="F395" s="3" t="n"/>
+      <c r="H395" s="3" t="n"/>
     </row>
     <row r="396">
       <c r="D396" s="2" t="n"/>
       <c r="F396" s="3" t="n"/>
+      <c r="H396" s="3" t="n"/>
     </row>
     <row r="397">
       <c r="D397" s="2" t="n"/>
       <c r="F397" s="3" t="n"/>
+      <c r="H397" s="3" t="n"/>
     </row>
     <row r="398">
       <c r="D398" s="2" t="n"/>
       <c r="F398" s="3" t="n"/>
+      <c r="H398" s="3" t="n"/>
     </row>
     <row r="399">
       <c r="D399" s="2" t="n"/>
       <c r="F399" s="3" t="n"/>
+      <c r="H399" s="3" t="n"/>
     </row>
     <row r="400">
       <c r="D400" s="2" t="n"/>
       <c r="F400" s="3" t="n"/>
+      <c r="H400" s="3" t="n"/>
     </row>
     <row r="401">
       <c r="D401" s="2" t="n"/>
       <c r="F401" s="3" t="n"/>
+      <c r="H401" s="3" t="n"/>
     </row>
     <row r="402">
       <c r="D402" s="2" t="n"/>
       <c r="F402" s="3" t="n"/>
+      <c r="H402" s="3" t="n"/>
     </row>
     <row r="403">
       <c r="D403" s="2" t="n"/>
       <c r="F403" s="3" t="n"/>
+      <c r="H403" s="3" t="n"/>
     </row>
     <row r="404">
       <c r="D404" s="2" t="n"/>
       <c r="F404" s="3" t="n"/>
+      <c r="H404" s="3" t="n"/>
     </row>
     <row r="405">
       <c r="D405" s="2" t="n"/>
       <c r="F405" s="3" t="n"/>
+      <c r="H405" s="3" t="n"/>
     </row>
     <row r="406">
       <c r="D406" s="2" t="n"/>
       <c r="F406" s="3" t="n"/>
+      <c r="H406" s="3" t="n"/>
     </row>
     <row r="407">
       <c r="D407" s="2" t="n"/>
       <c r="F407" s="3" t="n"/>
+      <c r="H407" s="3" t="n"/>
     </row>
     <row r="408">
       <c r="D408" s="2" t="n"/>
       <c r="F408" s="3" t="n"/>
+      <c r="H408" s="3" t="n"/>
     </row>
     <row r="409">
       <c r="D409" s="2" t="n"/>
       <c r="F409" s="3" t="n"/>
+      <c r="H409" s="3" t="n"/>
     </row>
     <row r="410">
       <c r="D410" s="2" t="n"/>
       <c r="F410" s="3" t="n"/>
+      <c r="H410" s="3" t="n"/>
     </row>
     <row r="411">
       <c r="D411" s="2" t="n"/>
       <c r="F411" s="3" t="n"/>
+      <c r="H411" s="3" t="n"/>
     </row>
     <row r="412">
       <c r="D412" s="2" t="n"/>
       <c r="F412" s="3" t="n"/>
+      <c r="H412" s="3" t="n"/>
     </row>
     <row r="413">
       <c r="D413" s="2" t="n"/>
       <c r="F413" s="3" t="n"/>
+      <c r="H413" s="3" t="n"/>
     </row>
     <row r="414">
       <c r="D414" s="2" t="n"/>
       <c r="F414" s="3" t="n"/>
+      <c r="H414" s="3" t="n"/>
     </row>
     <row r="415">
       <c r="D415" s="2" t="n"/>
       <c r="F415" s="3" t="n"/>
+      <c r="H415" s="3" t="n"/>
     </row>
     <row r="416">
       <c r="D416" s="2" t="n"/>
       <c r="F416" s="3" t="n"/>
+      <c r="H416" s="3" t="n"/>
     </row>
     <row r="417">
       <c r="D417" s="2" t="n"/>
       <c r="F417" s="3" t="n"/>
+      <c r="H417" s="3" t="n"/>
     </row>
     <row r="418">
       <c r="D418" s="2" t="n"/>
       <c r="F418" s="3" t="n"/>
+      <c r="H418" s="3" t="n"/>
     </row>
     <row r="419">
       <c r="D419" s="2" t="n"/>
       <c r="F419" s="3" t="n"/>
+      <c r="H419" s="3" t="n"/>
     </row>
     <row r="420">
       <c r="D420" s="2" t="n"/>
       <c r="F420" s="3" t="n"/>
+      <c r="H420" s="3" t="n"/>
     </row>
     <row r="421">
       <c r="D421" s="2" t="n"/>
       <c r="F421" s="3" t="n"/>
+      <c r="H421" s="3" t="n"/>
     </row>
     <row r="422">
       <c r="D422" s="2" t="n"/>
       <c r="F422" s="3" t="n"/>
+      <c r="H422" s="3" t="n"/>
     </row>
     <row r="423">
       <c r="D423" s="2" t="n"/>
       <c r="F423" s="3" t="n"/>
+      <c r="H423" s="3" t="n"/>
     </row>
     <row r="424">
       <c r="D424" s="2" t="n"/>
       <c r="F424" s="3" t="n"/>
+      <c r="H424" s="3" t="n"/>
     </row>
     <row r="425">
       <c r="D425" s="2" t="n"/>
       <c r="F425" s="3" t="n"/>
+      <c r="H425" s="3" t="n"/>
     </row>
     <row r="426">
       <c r="D426" s="2" t="n"/>
       <c r="F426" s="3" t="n"/>
+      <c r="H426" s="3" t="n"/>
     </row>
     <row r="427">
       <c r="D427" s="2" t="n"/>
       <c r="F427" s="3" t="n"/>
+      <c r="H427" s="3" t="n"/>
     </row>
     <row r="428">
       <c r="D428" s="2" t="n"/>
       <c r="F428" s="3" t="n"/>
+      <c r="H428" s="3" t="n"/>
     </row>
     <row r="429">
       <c r="D429" s="2" t="n"/>
       <c r="F429" s="3" t="n"/>
+      <c r="H429" s="3" t="n"/>
     </row>
     <row r="430">
       <c r="D430" s="2" t="n"/>
       <c r="F430" s="3" t="n"/>
+      <c r="H430" s="3" t="n"/>
     </row>
     <row r="431">
       <c r="D431" s="2" t="n"/>
       <c r="F431" s="3" t="n"/>
+      <c r="H431" s="3" t="n"/>
     </row>
     <row r="432">
       <c r="D432" s="2" t="n"/>
       <c r="F432" s="3" t="n"/>
+      <c r="H432" s="3" t="n"/>
     </row>
     <row r="433">
       <c r="D433" s="2" t="n"/>
       <c r="F433" s="3" t="n"/>
+      <c r="H433" s="3" t="n"/>
     </row>
     <row r="434">
       <c r="D434" s="2" t="n"/>
       <c r="F434" s="3" t="n"/>
+      <c r="H434" s="3" t="n"/>
     </row>
     <row r="435">
       <c r="D435" s="2" t="n"/>
       <c r="F435" s="3" t="n"/>
+      <c r="H435" s="3" t="n"/>
     </row>
     <row r="436">
       <c r="D436" s="2" t="n"/>
       <c r="F436" s="3" t="n"/>
+      <c r="H436" s="3" t="n"/>
     </row>
     <row r="437">
       <c r="D437" s="2" t="n"/>
       <c r="F437" s="3" t="n"/>
+      <c r="H437" s="3" t="n"/>
     </row>
     <row r="438">
       <c r="D438" s="2" t="n"/>
       <c r="F438" s="3" t="n"/>
+      <c r="H438" s="3" t="n"/>
     </row>
     <row r="439">
       <c r="D439" s="2" t="n"/>
       <c r="F439" s="3" t="n"/>
+      <c r="H439" s="3" t="n"/>
     </row>
     <row r="440">
       <c r="D440" s="2" t="n"/>
       <c r="F440" s="3" t="n"/>
+      <c r="H440" s="3" t="n"/>
     </row>
     <row r="441">
       <c r="D441" s="2" t="n"/>
       <c r="F441" s="3" t="n"/>
+      <c r="H441" s="3" t="n"/>
     </row>
     <row r="442">
       <c r="D442" s="2" t="n"/>
       <c r="F442" s="3" t="n"/>
+      <c r="H442" s="3" t="n"/>
     </row>
     <row r="443">
       <c r="D443" s="2" t="n"/>
       <c r="F443" s="3" t="n"/>
+      <c r="H443" s="3" t="n"/>
     </row>
     <row r="444">
       <c r="D444" s="2" t="n"/>
       <c r="F444" s="3" t="n"/>
+      <c r="H444" s="3" t="n"/>
     </row>
     <row r="445">
       <c r="D445" s="2" t="n"/>
       <c r="F445" s="3" t="n"/>
+      <c r="H445" s="3" t="n"/>
     </row>
     <row r="446">
       <c r="D446" s="2" t="n"/>
       <c r="F446" s="3" t="n"/>
+      <c r="H446" s="3" t="n"/>
     </row>
     <row r="447">
       <c r="D447" s="2" t="n"/>
       <c r="F447" s="3" t="n"/>
+      <c r="H447" s="3" t="n"/>
     </row>
     <row r="448">
       <c r="D448" s="2" t="n"/>
       <c r="F448" s="3" t="n"/>
+      <c r="H448" s="3" t="n"/>
     </row>
     <row r="449">
       <c r="D449" s="2" t="n"/>
       <c r="F449" s="3" t="n"/>
+      <c r="H449" s="3" t="n"/>
     </row>
     <row r="450">
       <c r="D450" s="2" t="n"/>
       <c r="F450" s="3" t="n"/>
+      <c r="H450" s="3" t="n"/>
     </row>
     <row r="451">
       <c r="D451" s="2" t="n"/>
       <c r="F451" s="3" t="n"/>
+      <c r="H451" s="3" t="n"/>
     </row>
     <row r="452">
       <c r="D452" s="2" t="n"/>
       <c r="F452" s="3" t="n"/>
+      <c r="H452" s="3" t="n"/>
     </row>
     <row r="453">
       <c r="D453" s="2" t="n"/>
       <c r="F453" s="3" t="n"/>
+      <c r="H453" s="3" t="n"/>
     </row>
     <row r="454">
       <c r="D454" s="2" t="n"/>
       <c r="F454" s="3" t="n"/>
+      <c r="H454" s="3" t="n"/>
     </row>
     <row r="455">
       <c r="D455" s="2" t="n"/>
       <c r="F455" s="3" t="n"/>
+      <c r="H455" s="3" t="n"/>
     </row>
     <row r="456">
       <c r="D456" s="2" t="n"/>
       <c r="F456" s="3" t="n"/>
+      <c r="H456" s="3" t="n"/>
     </row>
     <row r="457">
       <c r="D457" s="2" t="n"/>
       <c r="F457" s="3" t="n"/>
+      <c r="H457" s="3" t="n"/>
     </row>
     <row r="458">
       <c r="D458" s="2" t="n"/>
       <c r="F458" s="3" t="n"/>
+      <c r="H458" s="3" t="n"/>
     </row>
     <row r="459">
       <c r="D459" s="2" t="n"/>
       <c r="F459" s="3" t="n"/>
+      <c r="H459" s="3" t="n"/>
     </row>
     <row r="460">
       <c r="D460" s="2" t="n"/>
       <c r="F460" s="3" t="n"/>
+      <c r="H460" s="3" t="n"/>
     </row>
     <row r="461">
       <c r="D461" s="2" t="n"/>
       <c r="F461" s="3" t="n"/>
+      <c r="H461" s="3" t="n"/>
     </row>
     <row r="462">
       <c r="D462" s="2" t="n"/>
       <c r="F462" s="3" t="n"/>
+      <c r="H462" s="3" t="n"/>
     </row>
     <row r="463">
       <c r="D463" s="2" t="n"/>
       <c r="F463" s="3" t="n"/>
+      <c r="H463" s="3" t="n"/>
     </row>
     <row r="464">
       <c r="D464" s="2" t="n"/>
       <c r="F464" s="3" t="n"/>
+      <c r="H464" s="3" t="n"/>
     </row>
     <row r="465">
       <c r="D465" s="2" t="n"/>
       <c r="F465" s="3" t="n"/>
+      <c r="H465" s="3" t="n"/>
     </row>
     <row r="466">
       <c r="D466" s="2" t="n"/>
       <c r="F466" s="3" t="n"/>
+      <c r="H466" s="3" t="n"/>
     </row>
     <row r="467">
       <c r="D467" s="2" t="n"/>
       <c r="F467" s="3" t="n"/>
+      <c r="H467" s="3" t="n"/>
     </row>
     <row r="468">
       <c r="D468" s="2" t="n"/>
       <c r="F468" s="3" t="n"/>
+      <c r="H468" s="3" t="n"/>
     </row>
     <row r="469">
       <c r="D469" s="2" t="n"/>
       <c r="F469" s="3" t="n"/>
+      <c r="H469" s="3" t="n"/>
     </row>
     <row r="470">
       <c r="D470" s="2" t="n"/>
       <c r="F470" s="3" t="n"/>
+      <c r="H470" s="3" t="n"/>
     </row>
     <row r="471">
       <c r="D471" s="2" t="n"/>
       <c r="F471" s="3" t="n"/>
+      <c r="H471" s="3" t="n"/>
     </row>
     <row r="472">
       <c r="D472" s="2" t="n"/>
       <c r="F472" s="3" t="n"/>
+      <c r="H472" s="3" t="n"/>
     </row>
     <row r="473">
       <c r="D473" s="2" t="n"/>
       <c r="F473" s="3" t="n"/>
+      <c r="H473" s="3" t="n"/>
     </row>
     <row r="474">
       <c r="D474" s="2" t="n"/>
       <c r="F474" s="3" t="n"/>
+      <c r="H474" s="3" t="n"/>
     </row>
     <row r="475">
       <c r="D475" s="2" t="n"/>
       <c r="F475" s="3" t="n"/>
+      <c r="H475" s="3" t="n"/>
     </row>
     <row r="476">
       <c r="D476" s="2" t="n"/>
       <c r="F476" s="3" t="n"/>
+      <c r="H476" s="3" t="n"/>
     </row>
     <row r="477">
       <c r="D477" s="2" t="n"/>
       <c r="F477" s="3" t="n"/>
+      <c r="H477" s="3" t="n"/>
     </row>
     <row r="478">
       <c r="D478" s="2" t="n"/>
       <c r="F478" s="3" t="n"/>
+      <c r="H478" s="3" t="n"/>
     </row>
     <row r="479">
       <c r="D479" s="2" t="n"/>
       <c r="F479" s="3" t="n"/>
+      <c r="H479" s="3" t="n"/>
     </row>
     <row r="480">
       <c r="D480" s="2" t="n"/>
       <c r="F480" s="3" t="n"/>
+      <c r="H480" s="3" t="n"/>
     </row>
     <row r="481">
       <c r="D481" s="2" t="n"/>
       <c r="F481" s="3" t="n"/>
+      <c r="H481" s="3" t="n"/>
     </row>
     <row r="482">
       <c r="D482" s="2" t="n"/>
       <c r="F482" s="3" t="n"/>
+      <c r="H482" s="3" t="n"/>
     </row>
     <row r="483">
       <c r="D483" s="2" t="n"/>
       <c r="F483" s="3" t="n"/>
+      <c r="H483" s="3" t="n"/>
     </row>
     <row r="484">
       <c r="D484" s="2" t="n"/>
       <c r="F484" s="3" t="n"/>
+      <c r="H484" s="3" t="n"/>
     </row>
     <row r="485">
       <c r="D485" s="2" t="n"/>
       <c r="F485" s="3" t="n"/>
+      <c r="H485" s="3" t="n"/>
     </row>
     <row r="486">
       <c r="D486" s="2" t="n"/>
       <c r="F486" s="3" t="n"/>
+      <c r="H486" s="3" t="n"/>
     </row>
     <row r="487">
       <c r="D487" s="2" t="n"/>
       <c r="F487" s="3" t="n"/>
+      <c r="H487" s="3" t="n"/>
     </row>
     <row r="488">
       <c r="D488" s="2" t="n"/>
       <c r="F488" s="3" t="n"/>
+      <c r="H488" s="3" t="n"/>
     </row>
     <row r="489">
       <c r="D489" s="2" t="n"/>
       <c r="F489" s="3" t="n"/>
+      <c r="H489" s="3" t="n"/>
     </row>
     <row r="490">
       <c r="D490" s="2" t="n"/>
       <c r="F490" s="3" t="n"/>
+      <c r="H490" s="3" t="n"/>
     </row>
     <row r="491">
       <c r="D491" s="2" t="n"/>
       <c r="F491" s="3" t="n"/>
+      <c r="H491" s="3" t="n"/>
     </row>
     <row r="492">
       <c r="D492" s="2" t="n"/>
       <c r="F492" s="3" t="n"/>
+      <c r="H492" s="3" t="n"/>
     </row>
     <row r="493">
       <c r="D493" s="2" t="n"/>
       <c r="F493" s="3" t="n"/>
+      <c r="H493" s="3" t="n"/>
     </row>
     <row r="494">
       <c r="D494" s="2" t="n"/>
       <c r="F494" s="3" t="n"/>
+      <c r="H494" s="3" t="n"/>
     </row>
     <row r="495">
       <c r="D495" s="2" t="n"/>
       <c r="F495" s="3" t="n"/>
+      <c r="H495" s="3" t="n"/>
     </row>
     <row r="496">
       <c r="D496" s="2" t="n"/>
       <c r="F496" s="3" t="n"/>
+      <c r="H496" s="3" t="n"/>
     </row>
     <row r="497">
       <c r="D497" s="2" t="n"/>
       <c r="F497" s="3" t="n"/>
+      <c r="H497" s="3" t="n"/>
     </row>
     <row r="498">
       <c r="D498" s="2" t="n"/>
       <c r="F498" s="3" t="n"/>
+      <c r="H498" s="3" t="n"/>
     </row>
     <row r="499">
       <c r="D499" s="2" t="n"/>
       <c r="F499" s="3" t="n"/>
+      <c r="H499" s="3" t="n"/>
     </row>
     <row r="500">
       <c r="D500" s="2" t="n"/>
       <c r="F500" s="3" t="n"/>
+      <c r="H500" s="3" t="n"/>
     </row>
     <row r="501">
       <c r="D501" s="2" t="n"/>
       <c r="F501" s="3" t="n"/>
+      <c r="H501" s="3" t="n"/>
     </row>
     <row r="502">
       <c r="D502" s="2" t="n"/>
       <c r="F502" s="3" t="n"/>
+      <c r="H502" s="3" t="n"/>
     </row>
     <row r="503">
       <c r="D503" s="2" t="n"/>
       <c r="F503" s="3" t="n"/>
+      <c r="H503" s="3" t="n"/>
     </row>
     <row r="504">
       <c r="D504" s="2" t="n"/>
       <c r="F504" s="3" t="n"/>
+      <c r="H504" s="3" t="n"/>
     </row>
     <row r="505">
       <c r="D505" s="2" t="n"/>
       <c r="F505" s="3" t="n"/>
+      <c r="H505" s="3" t="n"/>
     </row>
     <row r="506">
       <c r="D506" s="2" t="n"/>
       <c r="F506" s="3" t="n"/>
+      <c r="H506" s="3" t="n"/>
     </row>
     <row r="507">
       <c r="D507" s="2" t="n"/>
       <c r="F507" s="3" t="n"/>
+      <c r="H507" s="3" t="n"/>
     </row>
     <row r="508">
       <c r="D508" s="2" t="n"/>
       <c r="F508" s="3" t="n"/>
+      <c r="H508" s="3" t="n"/>
     </row>
     <row r="509">
       <c r="D509" s="2" t="n"/>
       <c r="F509" s="3" t="n"/>
+      <c r="H509" s="3" t="n"/>
     </row>
     <row r="510">
       <c r="D510" s="2" t="n"/>
       <c r="F510" s="3" t="n"/>
+      <c r="H510" s="3" t="n"/>
     </row>
     <row r="511">
       <c r="D511" s="2" t="n"/>
       <c r="F511" s="3" t="n"/>
+      <c r="H511" s="3" t="n"/>
     </row>
     <row r="512">
       <c r="D512" s="2" t="n"/>
       <c r="F512" s="3" t="n"/>
+      <c r="H512" s="3" t="n"/>
     </row>
     <row r="513">
       <c r="D513" s="2" t="n"/>
       <c r="F513" s="3" t="n"/>
+      <c r="H513" s="3" t="n"/>
     </row>
     <row r="514">
       <c r="D514" s="2" t="n"/>
       <c r="F514" s="3" t="n"/>
+      <c r="H514" s="3" t="n"/>
     </row>
     <row r="515">
       <c r="D515" s="2" t="n"/>
       <c r="F515" s="3" t="n"/>
+      <c r="H515" s="3" t="n"/>
     </row>
     <row r="516">
       <c r="D516" s="2" t="n"/>
       <c r="F516" s="3" t="n"/>
+      <c r="H516" s="3" t="n"/>
     </row>
     <row r="517">
       <c r="D517" s="2" t="n"/>
       <c r="F517" s="3" t="n"/>
+      <c r="H517" s="3" t="n"/>
     </row>
     <row r="518">
       <c r="D518" s="2" t="n"/>
       <c r="F518" s="3" t="n"/>
+      <c r="H518" s="3" t="n"/>
     </row>
     <row r="519">
       <c r="D519" s="2" t="n"/>
       <c r="F519" s="3" t="n"/>
+      <c r="H519" s="3" t="n"/>
     </row>
     <row r="520">
       <c r="D520" s="2" t="n"/>
       <c r="F520" s="3" t="n"/>
+      <c r="H520" s="3" t="n"/>
     </row>
     <row r="521">
       <c r="D521" s="2" t="n"/>
       <c r="F521" s="3" t="n"/>
+      <c r="H521" s="3" t="n"/>
     </row>
     <row r="522">
       <c r="D522" s="2" t="n"/>
       <c r="F522" s="3" t="n"/>
+      <c r="H522" s="3" t="n"/>
     </row>
     <row r="523">
       <c r="D523" s="2" t="n"/>
       <c r="F523" s="3" t="n"/>
+      <c r="H523" s="3" t="n"/>
     </row>
     <row r="524">
       <c r="D524" s="2" t="n"/>
       <c r="F524" s="3" t="n"/>
+      <c r="H524" s="3" t="n"/>
     </row>
     <row r="525">
       <c r="D525" s="2" t="n"/>
       <c r="F525" s="3" t="n"/>
+      <c r="H525" s="3" t="n"/>
     </row>
     <row r="526">
       <c r="D526" s="2" t="n"/>
       <c r="F526" s="3" t="n"/>
+      <c r="H526" s="3" t="n"/>
     </row>
     <row r="527">
       <c r="D527" s="2" t="n"/>
       <c r="F527" s="3" t="n"/>
+      <c r="H527" s="3" t="n"/>
     </row>
     <row r="528">
       <c r="D528" s="2" t="n"/>
       <c r="F528" s="3" t="n"/>
+      <c r="H528" s="3" t="n"/>
     </row>
     <row r="529">
       <c r="D529" s="2" t="n"/>
       <c r="F529" s="3" t="n"/>
+      <c r="H529" s="3" t="n"/>
     </row>
     <row r="530">
       <c r="D530" s="2" t="n"/>
       <c r="F530" s="3" t="n"/>
+      <c r="H530" s="3" t="n"/>
     </row>
     <row r="531">
       <c r="D531" s="2" t="n"/>
       <c r="F531" s="3" t="n"/>
+      <c r="H531" s="3" t="n"/>
     </row>
     <row r="532">
       <c r="D532" s="2" t="n"/>
       <c r="F532" s="3" t="n"/>
+      <c r="H532" s="3" t="n"/>
     </row>
     <row r="533">
       <c r="D533" s="2" t="n"/>
       <c r="F533" s="3" t="n"/>
+      <c r="H533" s="3" t="n"/>
     </row>
     <row r="534">
       <c r="D534" s="2" t="n"/>
       <c r="F534" s="3" t="n"/>
+      <c r="H534" s="3" t="n"/>
     </row>
     <row r="535">
       <c r="D535" s="2" t="n"/>
       <c r="F535" s="3" t="n"/>
+      <c r="H535" s="3" t="n"/>
     </row>
     <row r="536">
       <c r="D536" s="2" t="n"/>
       <c r="F536" s="3" t="n"/>
+      <c r="H536" s="3" t="n"/>
     </row>
     <row r="537">
       <c r="D537" s="2" t="n"/>
       <c r="F537" s="3" t="n"/>
+      <c r="H537" s="3" t="n"/>
     </row>
     <row r="538">
       <c r="D538" s="2" t="n"/>
       <c r="F538" s="3" t="n"/>
+      <c r="H538" s="3" t="n"/>
     </row>
     <row r="539">
       <c r="D539" s="2" t="n"/>
       <c r="F539" s="3" t="n"/>
+      <c r="H539" s="3" t="n"/>
     </row>
     <row r="540">
       <c r="D540" s="2" t="n"/>
       <c r="F540" s="3" t="n"/>
+      <c r="H540" s="3" t="n"/>
     </row>
     <row r="541">
       <c r="D541" s="2" t="n"/>
       <c r="F541" s="3" t="n"/>
+      <c r="H541" s="3" t="n"/>
     </row>
     <row r="542">
       <c r="D542" s="2" t="n"/>
       <c r="F542" s="3" t="n"/>
+      <c r="H542" s="3" t="n"/>
     </row>
     <row r="543">
       <c r="D543" s="2" t="n"/>
       <c r="F543" s="3" t="n"/>
+      <c r="H543" s="3" t="n"/>
     </row>
     <row r="544">
       <c r="D544" s="2" t="n"/>
       <c r="F544" s="3" t="n"/>
+      <c r="H544" s="3" t="n"/>
     </row>
     <row r="545">
       <c r="D545" s="2" t="n"/>
       <c r="F545" s="3" t="n"/>
+      <c r="H545" s="3" t="n"/>
     </row>
     <row r="546">
       <c r="D546" s="2" t="n"/>
       <c r="F546" s="3" t="n"/>
+      <c r="H546" s="3" t="n"/>
     </row>
     <row r="547">
       <c r="D547" s="2" t="n"/>
       <c r="F547" s="3" t="n"/>
+      <c r="H547" s="3" t="n"/>
     </row>
     <row r="548">
       <c r="D548" s="2" t="n"/>
       <c r="F548" s="3" t="n"/>
+      <c r="H548" s="3" t="n"/>
     </row>
     <row r="549">
       <c r="D549" s="2" t="n"/>
       <c r="F549" s="3" t="n"/>
+      <c r="H549" s="3" t="n"/>
     </row>
     <row r="550">
       <c r="D550" s="2" t="n"/>
       <c r="F550" s="3" t="n"/>
+      <c r="H550" s="3" t="n"/>
     </row>
     <row r="551">
       <c r="D551" s="2" t="n"/>
       <c r="F551" s="3" t="n"/>
+      <c r="H551" s="3" t="n"/>
     </row>
     <row r="552">
       <c r="D552" s="2" t="n"/>
       <c r="F552" s="3" t="n"/>
+      <c r="H552" s="3" t="n"/>
     </row>
     <row r="553">
       <c r="D553" s="2" t="n"/>
       <c r="F553" s="3" t="n"/>
+      <c r="H553" s="3" t="n"/>
     </row>
     <row r="554">
       <c r="D554" s="2" t="n"/>
       <c r="F554" s="3" t="n"/>
+      <c r="H554" s="3" t="n"/>
     </row>
     <row r="555">
       <c r="D555" s="2" t="n"/>
       <c r="F555" s="3" t="n"/>
+      <c r="H555" s="3" t="n"/>
     </row>
     <row r="556">
       <c r="D556" s="2" t="n"/>
       <c r="F556" s="3" t="n"/>
+      <c r="H556" s="3" t="n"/>
     </row>
     <row r="557">
       <c r="D557" s="2" t="n"/>
       <c r="F557" s="3" t="n"/>
+      <c r="H557" s="3" t="n"/>
     </row>
     <row r="558">
       <c r="D558" s="2" t="n"/>
       <c r="F558" s="3" t="n"/>
+      <c r="H558" s="3" t="n"/>
     </row>
     <row r="559">
       <c r="D559" s="2" t="n"/>
       <c r="F559" s="3" t="n"/>
+      <c r="H559" s="3" t="n"/>
     </row>
     <row r="560">
       <c r="D560" s="2" t="n"/>
       <c r="F560" s="3" t="n"/>
+      <c r="H560" s="3" t="n"/>
     </row>
     <row r="561">
       <c r="D561" s="2" t="n"/>
       <c r="F561" s="3" t="n"/>
+      <c r="H561" s="3" t="n"/>
     </row>
     <row r="562">
       <c r="D562" s="2" t="n"/>
       <c r="F562" s="3" t="n"/>
+      <c r="H562" s="3" t="n"/>
     </row>
     <row r="563">
       <c r="D563" s="2" t="n"/>
       <c r="F563" s="3" t="n"/>
+      <c r="H563" s="3" t="n"/>
     </row>
     <row r="564">
       <c r="D564" s="2" t="n"/>
       <c r="F564" s="3" t="n"/>
+      <c r="H564" s="3" t="n"/>
     </row>
     <row r="565">
       <c r="D565" s="2" t="n"/>
       <c r="F565" s="3" t="n"/>
+      <c r="H565" s="3" t="n"/>
     </row>
     <row r="566">
       <c r="D566" s="2" t="n"/>
       <c r="F566" s="3" t="n"/>
+      <c r="H566" s="3" t="n"/>
     </row>
     <row r="567">
       <c r="D567" s="2" t="n"/>
       <c r="F567" s="3" t="n"/>
+      <c r="H567" s="3" t="n"/>
     </row>
     <row r="568">
       <c r="D568" s="2" t="n"/>
       <c r="F568" s="3" t="n"/>
+      <c r="H568" s="3" t="n"/>
     </row>
     <row r="569">
       <c r="D569" s="2" t="n"/>
       <c r="F569" s="3" t="n"/>
+      <c r="H569" s="3" t="n"/>
     </row>
     <row r="570">
       <c r="D570" s="2" t="n"/>
       <c r="F570" s="3" t="n"/>
+      <c r="H570" s="3" t="n"/>
     </row>
     <row r="571">
       <c r="D571" s="2" t="n"/>
       <c r="F571" s="3" t="n"/>
+      <c r="H571" s="3" t="n"/>
     </row>
     <row r="572">
       <c r="D572" s="2" t="n"/>
       <c r="F572" s="3" t="n"/>
+      <c r="H572" s="3" t="n"/>
     </row>
     <row r="573">
       <c r="D573" s="2" t="n"/>
       <c r="F573" s="3" t="n"/>
+      <c r="H573" s="3" t="n"/>
     </row>
     <row r="574">
       <c r="D574" s="2" t="n"/>
       <c r="F574" s="3" t="n"/>
+      <c r="H574" s="3" t="n"/>
     </row>
     <row r="575">
       <c r="D575" s="2" t="n"/>
       <c r="F575" s="3" t="n"/>
+      <c r="H575" s="3" t="n"/>
     </row>
     <row r="576">
       <c r="D576" s="2" t="n"/>
       <c r="F576" s="3" t="n"/>
+      <c r="H576" s="3" t="n"/>
     </row>
     <row r="577">
       <c r="D577" s="2" t="n"/>
       <c r="F577" s="3" t="n"/>
+      <c r="H577" s="3" t="n"/>
     </row>
     <row r="578">
       <c r="D578" s="2" t="n"/>
       <c r="F578" s="3" t="n"/>
+      <c r="H578" s="3" t="n"/>
     </row>
     <row r="579">
       <c r="D579" s="2" t="n"/>
       <c r="F579" s="3" t="n"/>
+      <c r="H579" s="3" t="n"/>
     </row>
     <row r="580">
       <c r="D580" s="2" t="n"/>
       <c r="F580" s="3" t="n"/>
+      <c r="H580" s="3" t="n"/>
     </row>
     <row r="581">
       <c r="D581" s="2" t="n"/>
       <c r="F581" s="3" t="n"/>
+      <c r="H581" s="3" t="n"/>
     </row>
     <row r="582">
       <c r="D582" s="2" t="n"/>
       <c r="F582" s="3" t="n"/>
+      <c r="H582" s="3" t="n"/>
     </row>
     <row r="583">
       <c r="D583" s="2" t="n"/>
       <c r="F583" s="3" t="n"/>
+      <c r="H583" s="3" t="n"/>
     </row>
     <row r="584">
       <c r="D584" s="2" t="n"/>
       <c r="F584" s="3" t="n"/>
+      <c r="H584" s="3" t="n"/>
     </row>
     <row r="585">
       <c r="D585" s="2" t="n"/>
       <c r="F585" s="3" t="n"/>
+      <c r="H585" s="3" t="n"/>
     </row>
     <row r="586">
       <c r="D586" s="2" t="n"/>
       <c r="F586" s="3" t="n"/>
+      <c r="H586" s="3" t="n"/>
     </row>
     <row r="587">
       <c r="D587" s="2" t="n"/>
       <c r="F587" s="3" t="n"/>
+      <c r="H587" s="3" t="n"/>
     </row>
     <row r="588">
       <c r="D588" s="2" t="n"/>
       <c r="F588" s="3" t="n"/>
+      <c r="H588" s="3" t="n"/>
     </row>
     <row r="589">
       <c r="D589" s="2" t="n"/>
       <c r="F589" s="3" t="n"/>
+      <c r="H589" s="3" t="n"/>
     </row>
     <row r="590">
       <c r="D590" s="2" t="n"/>
       <c r="F590" s="3" t="n"/>
+      <c r="H590" s="3" t="n"/>
     </row>
     <row r="591">
       <c r="D591" s="2" t="n"/>
       <c r="F591" s="3" t="n"/>
+      <c r="H591" s="3" t="n"/>
     </row>
     <row r="592">
       <c r="D592" s="2" t="n"/>
       <c r="F592" s="3" t="n"/>
+      <c r="H592" s="3" t="n"/>
     </row>
     <row r="593">
       <c r="D593" s="2" t="n"/>
       <c r="F593" s="3" t="n"/>
+      <c r="H593" s="3" t="n"/>
     </row>
     <row r="594">
       <c r="D594" s="2" t="n"/>
       <c r="F594" s="3" t="n"/>
+      <c r="H594" s="3" t="n"/>
     </row>
     <row r="595">
       <c r="D595" s="2" t="n"/>
       <c r="F595" s="3" t="n"/>
+      <c r="H595" s="3" t="n"/>
     </row>
     <row r="596">
       <c r="D596" s="2" t="n"/>
       <c r="F596" s="3" t="n"/>
+      <c r="H596" s="3" t="n"/>
     </row>
     <row r="597">
       <c r="D597" s="2" t="n"/>
       <c r="F597" s="3" t="n"/>
+      <c r="H597" s="3" t="n"/>
     </row>
     <row r="598">
       <c r="D598" s="2" t="n"/>
       <c r="F598" s="3" t="n"/>
+      <c r="H598" s="3" t="n"/>
     </row>
     <row r="599">
       <c r="D599" s="2" t="n"/>
       <c r="F599" s="3" t="n"/>
+      <c r="H599" s="3" t="n"/>
     </row>
     <row r="600">
       <c r="D600" s="2" t="n"/>
       <c r="F600" s="3" t="n"/>
+      <c r="H600" s="3" t="n"/>
     </row>
     <row r="601">
       <c r="D601" s="2" t="n"/>
       <c r="F601" s="3" t="n"/>
+      <c r="H601" s="3" t="n"/>
     </row>
     <row r="602">
       <c r="D602" s="2" t="n"/>
       <c r="F602" s="3" t="n"/>
+      <c r="H602" s="3" t="n"/>
     </row>
     <row r="603">
       <c r="D603" s="2" t="n"/>
       <c r="F603" s="3" t="n"/>
+      <c r="H603" s="3" t="n"/>
     </row>
     <row r="604">
       <c r="D604" s="2" t="n"/>
       <c r="F604" s="3" t="n"/>
+      <c r="H604" s="3" t="n"/>
     </row>
     <row r="605">
       <c r="D605" s="2" t="n"/>
       <c r="F605" s="3" t="n"/>
+      <c r="H605" s="3" t="n"/>
     </row>
     <row r="606">
       <c r="D606" s="2" t="n"/>
       <c r="F606" s="3" t="n"/>
+      <c r="H606" s="3" t="n"/>
     </row>
     <row r="607">
       <c r="D607" s="2" t="n"/>
       <c r="F607" s="3" t="n"/>
+      <c r="H607" s="3" t="n"/>
     </row>
     <row r="608">
       <c r="D608" s="2" t="n"/>
       <c r="F608" s="3" t="n"/>
+      <c r="H608" s="3" t="n"/>
     </row>
     <row r="609">
       <c r="D609" s="2" t="n"/>
       <c r="F609" s="3" t="n"/>
+      <c r="H609" s="3" t="n"/>
     </row>
     <row r="610">
       <c r="D610" s="2" t="n"/>
       <c r="F610" s="3" t="n"/>
+      <c r="H610" s="3" t="n"/>
     </row>
     <row r="611">
       <c r="D611" s="2" t="n"/>
       <c r="F611" s="3" t="n"/>
+      <c r="H611" s="3" t="n"/>
     </row>
     <row r="612">
       <c r="D612" s="2" t="n"/>
       <c r="F612" s="3" t="n"/>
+      <c r="H612" s="3" t="n"/>
     </row>
     <row r="613">
       <c r="D613" s="2" t="n"/>
       <c r="F613" s="3" t="n"/>
+      <c r="H613" s="3" t="n"/>
     </row>
     <row r="614">
       <c r="D614" s="2" t="n"/>
       <c r="F614" s="3" t="n"/>
+      <c r="H614" s="3" t="n"/>
     </row>
     <row r="615">
       <c r="D615" s="2" t="n"/>
       <c r="F615" s="3" t="n"/>
+      <c r="H615" s="3" t="n"/>
     </row>
     <row r="616">
       <c r="D616" s="2" t="n"/>
       <c r="F616" s="3" t="n"/>
+      <c r="H616" s="3" t="n"/>
     </row>
     <row r="617">
       <c r="D617" s="2" t="n"/>
       <c r="F617" s="3" t="n"/>
+      <c r="H617" s="3" t="n"/>
     </row>
     <row r="618">
       <c r="D618" s="2" t="n"/>
       <c r="F618" s="3" t="n"/>
+      <c r="H618" s="3" t="n"/>
     </row>
     <row r="619">
       <c r="D619" s="2" t="n"/>
       <c r="F619" s="3" t="n"/>
+      <c r="H619" s="3" t="n"/>
     </row>
     <row r="620">
       <c r="D620" s="2" t="n"/>
       <c r="F620" s="3" t="n"/>
+      <c r="H620" s="3" t="n"/>
     </row>
     <row r="621">
       <c r="D621" s="2" t="n"/>
       <c r="F621" s="3" t="n"/>
+      <c r="H621" s="3" t="n"/>
     </row>
     <row r="622">
       <c r="D622" s="2" t="n"/>
       <c r="F622" s="3" t="n"/>
+      <c r="H622" s="3" t="n"/>
     </row>
     <row r="623">
       <c r="D623" s="2" t="n"/>
       <c r="F623" s="3" t="n"/>
+      <c r="H623" s="3" t="n"/>
     </row>
     <row r="624">
       <c r="D624" s="2" t="n"/>
       <c r="F624" s="3" t="n"/>
+      <c r="H624" s="3" t="n"/>
     </row>
     <row r="625">
       <c r="D625" s="2" t="n"/>
       <c r="F625" s="3" t="n"/>
+      <c r="H625" s="3" t="n"/>
     </row>
     <row r="626">
       <c r="D626" s="2" t="n"/>
       <c r="F626" s="3" t="n"/>
+      <c r="H626" s="3" t="n"/>
     </row>
     <row r="627">
       <c r="D627" s="2" t="n"/>
       <c r="F627" s="3" t="n"/>
+      <c r="H627" s="3" t="n"/>
     </row>
     <row r="628">
       <c r="D628" s="2" t="n"/>
       <c r="F628" s="3" t="n"/>
+      <c r="H628" s="3" t="n"/>
     </row>
     <row r="629">
       <c r="D629" s="2" t="n"/>
       <c r="F629" s="3" t="n"/>
+      <c r="H629" s="3" t="n"/>
     </row>
     <row r="630">
       <c r="D630" s="2" t="n"/>
       <c r="F630" s="3" t="n"/>
+      <c r="H630" s="3" t="n"/>
     </row>
     <row r="631">
       <c r="D631" s="2" t="n"/>
       <c r="F631" s="3" t="n"/>
+      <c r="H631" s="3" t="n"/>
     </row>
     <row r="632">
       <c r="D632" s="2" t="n"/>
       <c r="F632" s="3" t="n"/>
+      <c r="H632" s="3" t="n"/>
     </row>
     <row r="633">
       <c r="D633" s="2" t="n"/>
       <c r="F633" s="3" t="n"/>
+      <c r="H633" s="3" t="n"/>
     </row>
     <row r="634">
       <c r="D634" s="2" t="n"/>
       <c r="F634" s="3" t="n"/>
+      <c r="H634" s="3" t="n"/>
     </row>
     <row r="635">
       <c r="D635" s="2" t="n"/>
       <c r="F635" s="3" t="n"/>
+      <c r="H635" s="3" t="n"/>
     </row>
     <row r="636">
       <c r="D636" s="2" t="n"/>
       <c r="F636" s="3" t="n"/>
+      <c r="H636" s="3" t="n"/>
     </row>
     <row r="637">
       <c r="D637" s="2" t="n"/>
       <c r="F637" s="3" t="n"/>
+      <c r="H637" s="3" t="n"/>
     </row>
     <row r="638">
       <c r="D638" s="2" t="n"/>
       <c r="F638" s="3" t="n"/>
+      <c r="H638" s="3" t="n"/>
     </row>
     <row r="639">
       <c r="D639" s="2" t="n"/>
       <c r="F639" s="3" t="n"/>
+      <c r="H639" s="3" t="n"/>
     </row>
     <row r="640">
       <c r="D640" s="2" t="n"/>
       <c r="F640" s="3" t="n"/>
+      <c r="H640" s="3" t="n"/>
     </row>
     <row r="641">
       <c r="D641" s="2" t="n"/>
       <c r="F641" s="3" t="n"/>
+      <c r="H641" s="3" t="n"/>
     </row>
     <row r="642">
       <c r="D642" s="2" t="n"/>
       <c r="F642" s="3" t="n"/>
+      <c r="H642" s="3" t="n"/>
     </row>
     <row r="643">
       <c r="D643" s="2" t="n"/>
       <c r="F643" s="3" t="n"/>
+      <c r="H643" s="3" t="n"/>
     </row>
     <row r="644">
       <c r="D644" s="2" t="n"/>
       <c r="F644" s="3" t="n"/>
+      <c r="H644" s="3" t="n"/>
     </row>
     <row r="645">
       <c r="D645" s="2" t="n"/>
       <c r="F645" s="3" t="n"/>
+      <c r="H645" s="3" t="n"/>
     </row>
     <row r="646">
       <c r="D646" s="2" t="n"/>
       <c r="F646" s="3" t="n"/>
+      <c r="H646" s="3" t="n"/>
     </row>
     <row r="647">
       <c r="D647" s="2" t="n"/>
       <c r="F647" s="3" t="n"/>
+      <c r="H647" s="3" t="n"/>
     </row>
     <row r="648">
       <c r="D648" s="2" t="n"/>
       <c r="F648" s="3" t="n"/>
+      <c r="H648" s="3" t="n"/>
     </row>
     <row r="649">
       <c r="D649" s="2" t="n"/>
       <c r="F649" s="3" t="n"/>
+      <c r="H649" s="3" t="n"/>
     </row>
     <row r="650">
       <c r="D650" s="2" t="n"/>
       <c r="F650" s="3" t="n"/>
+      <c r="H650" s="3" t="n"/>
     </row>
     <row r="651">
       <c r="D651" s="2" t="n"/>
       <c r="F651" s="3" t="n"/>
+      <c r="H651" s="3" t="n"/>
     </row>
     <row r="652">
       <c r="D652" s="2" t="n"/>
       <c r="F652" s="3" t="n"/>
+      <c r="H652" s="3" t="n"/>
     </row>
     <row r="653">
       <c r="D653" s="2" t="n"/>
       <c r="F653" s="3" t="n"/>
+      <c r="H653" s="3" t="n"/>
     </row>
     <row r="654">
       <c r="D654" s="2" t="n"/>
       <c r="F654" s="3" t="n"/>
+      <c r="H654" s="3" t="n"/>
     </row>
     <row r="655">
       <c r="D655" s="2" t="n"/>
       <c r="F655" s="3" t="n"/>
+      <c r="H655" s="3" t="n"/>
     </row>
     <row r="656">
       <c r="D656" s="2" t="n"/>
       <c r="F656" s="3" t="n"/>
+      <c r="H656" s="3" t="n"/>
     </row>
     <row r="657">
       <c r="D657" s="2" t="n"/>
       <c r="F657" s="3" t="n"/>
+      <c r="H657" s="3" t="n"/>
     </row>
     <row r="658">
       <c r="D658" s="2" t="n"/>
       <c r="F658" s="3" t="n"/>
+      <c r="H658" s="3" t="n"/>
     </row>
     <row r="659">
       <c r="D659" s="2" t="n"/>
       <c r="F659" s="3" t="n"/>
+      <c r="H659" s="3" t="n"/>
     </row>
     <row r="660">
       <c r="D660" s="2" t="n"/>
       <c r="F660" s="3" t="n"/>
+      <c r="H660" s="3" t="n"/>
     </row>
     <row r="661">
       <c r="D661" s="2" t="n"/>
       <c r="F661" s="3" t="n"/>
+      <c r="H661" s="3" t="n"/>
     </row>
     <row r="662">
       <c r="D662" s="2" t="n"/>
       <c r="F662" s="3" t="n"/>
+      <c r="H662" s="3" t="n"/>
     </row>
     <row r="663">
       <c r="D663" s="2" t="n"/>
       <c r="F663" s="3" t="n"/>
+      <c r="H663" s="3" t="n"/>
     </row>
     <row r="664">
       <c r="D664" s="2" t="n"/>
       <c r="F664" s="3" t="n"/>
+      <c r="H664" s="3" t="n"/>
     </row>
     <row r="665">
       <c r="D665" s="2" t="n"/>
       <c r="F665" s="3" t="n"/>
+      <c r="H665" s="3" t="n"/>
     </row>
     <row r="666">
       <c r="D666" s="2" t="n"/>
       <c r="F666" s="3" t="n"/>
+      <c r="H666" s="3" t="n"/>
     </row>
     <row r="667">
       <c r="D667" s="2" t="n"/>
       <c r="F667" s="3" t="n"/>
+      <c r="H667" s="3" t="n"/>
     </row>
     <row r="668">
       <c r="D668" s="2" t="n"/>
       <c r="F668" s="3" t="n"/>
+      <c r="H668" s="3" t="n"/>
     </row>
     <row r="669">
       <c r="D669" s="2" t="n"/>
       <c r="F669" s="3" t="n"/>
+      <c r="H669" s="3" t="n"/>
     </row>
     <row r="670">
       <c r="D670" s="2" t="n"/>
       <c r="F670" s="3" t="n"/>
+      <c r="H670" s="3" t="n"/>
     </row>
     <row r="671">
       <c r="D671" s="2" t="n"/>
       <c r="F671" s="3" t="n"/>
+      <c r="H671" s="3" t="n"/>
     </row>
     <row r="672">
       <c r="D672" s="2" t="n"/>
       <c r="F672" s="3" t="n"/>
+      <c r="H672" s="3" t="n"/>
     </row>
     <row r="673">
       <c r="D673" s="2" t="n"/>
       <c r="F673" s="3" t="n"/>
+      <c r="H673" s="3" t="n"/>
     </row>
     <row r="674">
       <c r="D674" s="2" t="n"/>
       <c r="F674" s="3" t="n"/>
+      <c r="H674" s="3" t="n"/>
     </row>
     <row r="675">
       <c r="D675" s="2" t="n"/>
       <c r="F675" s="3" t="n"/>
+      <c r="H675" s="3" t="n"/>
     </row>
     <row r="676">
       <c r="D676" s="2" t="n"/>
       <c r="F676" s="3" t="n"/>
+      <c r="H676" s="3" t="n"/>
     </row>
     <row r="677">
       <c r="D677" s="2" t="n"/>
       <c r="F677" s="3" t="n"/>
+      <c r="H677" s="3" t="n"/>
     </row>
     <row r="678">
       <c r="D678" s="2" t="n"/>
       <c r="F678" s="3" t="n"/>
+      <c r="H678" s="3" t="n"/>
     </row>
     <row r="679">
       <c r="D679" s="2" t="n"/>
       <c r="F679" s="3" t="n"/>
+      <c r="H679" s="3" t="n"/>
     </row>
     <row r="680">
       <c r="D680" s="2" t="n"/>
       <c r="F680" s="3" t="n"/>
+      <c r="H680" s="3" t="n"/>
     </row>
     <row r="681">
       <c r="D681" s="2" t="n"/>
       <c r="F681" s="3" t="n"/>
+      <c r="H681" s="3" t="n"/>
     </row>
     <row r="682">
       <c r="D682" s="2" t="n"/>
       <c r="F682" s="3" t="n"/>
+      <c r="H682" s="3" t="n"/>
     </row>
     <row r="683">
       <c r="D683" s="2" t="n"/>
       <c r="F683" s="3" t="n"/>
+      <c r="H683" s="3" t="n"/>
     </row>
     <row r="684">
       <c r="D684" s="2" t="n"/>
       <c r="F684" s="3" t="n"/>
+      <c r="H684" s="3" t="n"/>
     </row>
     <row r="685">
       <c r="D685" s="2" t="n"/>
       <c r="F685" s="3" t="n"/>
+      <c r="H685" s="3" t="n"/>
     </row>
     <row r="686">
       <c r="D686" s="2" t="n"/>
       <c r="F686" s="3" t="n"/>
+      <c r="H686" s="3" t="n"/>
     </row>
     <row r="687">
       <c r="D687" s="2" t="n"/>
       <c r="F687" s="3" t="n"/>
+      <c r="H687" s="3" t="n"/>
     </row>
     <row r="688">
       <c r="D688" s="2" t="n"/>
       <c r="F688" s="3" t="n"/>
+      <c r="H688" s="3" t="n"/>
     </row>
     <row r="689">
       <c r="D689" s="2" t="n"/>
       <c r="F689" s="3" t="n"/>
+      <c r="H689" s="3" t="n"/>
     </row>
     <row r="690">
       <c r="D690" s="2" t="n"/>
       <c r="F690" s="3" t="n"/>
+      <c r="H690" s="3" t="n"/>
     </row>
     <row r="691">
       <c r="D691" s="2" t="n"/>
       <c r="F691" s="3" t="n"/>
+      <c r="H691" s="3" t="n"/>
     </row>
     <row r="692">
       <c r="D692" s="2" t="n"/>
       <c r="F692" s="3" t="n"/>
+      <c r="H692" s="3" t="n"/>
     </row>
     <row r="693">
       <c r="D693" s="2" t="n"/>
       <c r="F693" s="3" t="n"/>
+      <c r="H693" s="3" t="n"/>
     </row>
     <row r="694">
       <c r="D694" s="2" t="n"/>
       <c r="F694" s="3" t="n"/>
+      <c r="H694" s="3" t="n"/>
     </row>
     <row r="695">
       <c r="D695" s="2" t="n"/>
       <c r="F695" s="3" t="n"/>
+      <c r="H695" s="3" t="n"/>
     </row>
     <row r="696">
       <c r="D696" s="2" t="n"/>
       <c r="F696" s="3" t="n"/>
+      <c r="H696" s="3" t="n"/>
     </row>
     <row r="697">
       <c r="D697" s="2" t="n"/>
       <c r="F697" s="3" t="n"/>
+      <c r="H697" s="3" t="n"/>
     </row>
     <row r="698">
       <c r="D698" s="2" t="n"/>
       <c r="F698" s="3" t="n"/>
+      <c r="H698" s="3" t="n"/>
     </row>
     <row r="699">
       <c r="D699" s="2" t="n"/>
       <c r="F699" s="3" t="n"/>
+      <c r="H699" s="3" t="n"/>
     </row>
     <row r="700">
       <c r="D700" s="2" t="n"/>
       <c r="F700" s="3" t="n"/>
+      <c r="H700" s="3" t="n"/>
     </row>
     <row r="701">
       <c r="D701" s="2" t="n"/>
       <c r="F701" s="3" t="n"/>
+      <c r="H701" s="3" t="n"/>
     </row>
     <row r="702">
       <c r="D702" s="2" t="n"/>
       <c r="F702" s="3" t="n"/>
+      <c r="H702" s="3" t="n"/>
     </row>
     <row r="703">
       <c r="D703" s="2" t="n"/>
       <c r="F703" s="3" t="n"/>
+      <c r="H703" s="3" t="n"/>
     </row>
     <row r="704">
       <c r="D704" s="2" t="n"/>
       <c r="F704" s="3" t="n"/>
+      <c r="H704" s="3" t="n"/>
     </row>
     <row r="705">
       <c r="D705" s="2" t="n"/>
       <c r="F705" s="3" t="n"/>
+      <c r="H705" s="3" t="n"/>
     </row>
     <row r="706">
       <c r="D706" s="2" t="n"/>
       <c r="F706" s="3" t="n"/>
+      <c r="H706" s="3" t="n"/>
     </row>
     <row r="707">
       <c r="D707" s="2" t="n"/>
       <c r="F707" s="3" t="n"/>
+      <c r="H707" s="3" t="n"/>
     </row>
     <row r="708">
       <c r="D708" s="2" t="n"/>
       <c r="F708" s="3" t="n"/>
+      <c r="H708" s="3" t="n"/>
     </row>
     <row r="709">
       <c r="D709" s="2" t="n"/>
       <c r="F709" s="3" t="n"/>
+      <c r="H709" s="3" t="n"/>
     </row>
     <row r="710">
       <c r="D710" s="2" t="n"/>
       <c r="F710" s="3" t="n"/>
+      <c r="H710" s="3" t="n"/>
     </row>
     <row r="711">
       <c r="D711" s="2" t="n"/>
       <c r="F711" s="3" t="n"/>
+      <c r="H711" s="3" t="n"/>
     </row>
     <row r="712">
       <c r="D712" s="2" t="n"/>
       <c r="F712" s="3" t="n"/>
+      <c r="H712" s="3" t="n"/>
     </row>
     <row r="713">
       <c r="D713" s="2" t="n"/>
       <c r="F713" s="3" t="n"/>
+      <c r="H713" s="3" t="n"/>
     </row>
     <row r="714">
       <c r="D714" s="2" t="n"/>
       <c r="F714" s="3" t="n"/>
+      <c r="H714" s="3" t="n"/>
     </row>
     <row r="715">
       <c r="D715" s="2" t="n"/>
       <c r="F715" s="3" t="n"/>
+      <c r="H715" s="3" t="n"/>
     </row>
     <row r="716">
       <c r="D716" s="2" t="n"/>
       <c r="F716" s="3" t="n"/>
+      <c r="H716" s="3" t="n"/>
     </row>
     <row r="717">
       <c r="D717" s="2" t="n"/>
       <c r="F717" s="3" t="n"/>
+      <c r="H717" s="3" t="n"/>
     </row>
     <row r="718">
       <c r="D718" s="2" t="n"/>
       <c r="F718" s="3" t="n"/>
+      <c r="H718" s="3" t="n"/>
     </row>
     <row r="719">
       <c r="D719" s="2" t="n"/>
       <c r="F719" s="3" t="n"/>
+      <c r="H719" s="3" t="n"/>
     </row>
     <row r="720">
       <c r="D720" s="2" t="n"/>
       <c r="F720" s="3" t="n"/>
+      <c r="H720" s="3" t="n"/>
     </row>
     <row r="721">
       <c r="D721" s="2" t="n"/>
       <c r="F721" s="3" t="n"/>
+      <c r="H721" s="3" t="n"/>
     </row>
     <row r="722">
       <c r="D722" s="2" t="n"/>
       <c r="F722" s="3" t="n"/>
+      <c r="H722" s="3" t="n"/>
     </row>
     <row r="723">
       <c r="D723" s="2" t="n"/>
       <c r="F723" s="3" t="n"/>
+      <c r="H723" s="3" t="n"/>
     </row>
     <row r="724">
       <c r="D724" s="2" t="n"/>
       <c r="F724" s="3" t="n"/>
+      <c r="H724" s="3" t="n"/>
     </row>
     <row r="725">
       <c r="D725" s="2" t="n"/>
       <c r="F725" s="3" t="n"/>
+      <c r="H725" s="3" t="n"/>
     </row>
     <row r="726">
       <c r="D726" s="2" t="n"/>
       <c r="F726" s="3" t="n"/>
+      <c r="H726" s="3" t="n"/>
     </row>
     <row r="727">
       <c r="D727" s="2" t="n"/>
       <c r="F727" s="3" t="n"/>
+      <c r="H727" s="3" t="n"/>
     </row>
     <row r="728">
       <c r="D728" s="2" t="n"/>
       <c r="F728" s="3" t="n"/>
+      <c r="H728" s="3" t="n"/>
     </row>
     <row r="729">
       <c r="D729" s="2" t="n"/>
       <c r="F729" s="3" t="n"/>
+      <c r="H729" s="3" t="n"/>
     </row>
     <row r="730">
       <c r="D730" s="2" t="n"/>
       <c r="F730" s="3" t="n"/>
+      <c r="H730" s="3" t="n"/>
     </row>
     <row r="731">
       <c r="D731" s="2" t="n"/>
       <c r="F731" s="3" t="n"/>
+      <c r="H731" s="3" t="n"/>
     </row>
     <row r="732">
       <c r="D732" s="2" t="n"/>
       <c r="F732" s="3" t="n"/>
+      <c r="H732" s="3" t="n"/>
     </row>
     <row r="733">
       <c r="D733" s="2" t="n"/>
       <c r="F733" s="3" t="n"/>
+      <c r="H733" s="3" t="n"/>
     </row>
     <row r="734">
       <c r="D734" s="2" t="n"/>
       <c r="F734" s="3" t="n"/>
+      <c r="H734" s="3" t="n"/>
     </row>
     <row r="735">
       <c r="D735" s="2" t="n"/>
       <c r="F735" s="3" t="n"/>
+      <c r="H735" s="3" t="n"/>
     </row>
     <row r="736">
       <c r="D736" s="2" t="n"/>
       <c r="F736" s="3" t="n"/>
+      <c r="H736" s="3" t="n"/>
     </row>
     <row r="737">
       <c r="D737" s="2" t="n"/>
       <c r="F737" s="3" t="n"/>
+      <c r="H737" s="3" t="n"/>
     </row>
     <row r="738">
       <c r="D738" s="2" t="n"/>
       <c r="F738" s="3" t="n"/>
+      <c r="H738" s="3" t="n"/>
     </row>
     <row r="739">
       <c r="D739" s="2" t="n"/>
       <c r="F739" s="3" t="n"/>
+      <c r="H739" s="3" t="n"/>
     </row>
     <row r="740">
       <c r="D740" s="2" t="n"/>
       <c r="F740" s="3" t="n"/>
+      <c r="H740" s="3" t="n"/>
     </row>
     <row r="741">
       <c r="D741" s="2" t="n"/>
       <c r="F741" s="3" t="n"/>
+      <c r="H741" s="3" t="n"/>
     </row>
     <row r="742">
       <c r="D742" s="2" t="n"/>
       <c r="F742" s="3" t="n"/>
+      <c r="H742" s="3" t="n"/>
     </row>
     <row r="743">
       <c r="D743" s="2" t="n"/>
       <c r="F743" s="3" t="n"/>
+      <c r="H743" s="3" t="n"/>
     </row>
     <row r="744">
       <c r="D744" s="2" t="n"/>
       <c r="F744" s="3" t="n"/>
+      <c r="H744" s="3" t="n"/>
     </row>
     <row r="745">
       <c r="D745" s="2" t="n"/>
       <c r="F745" s="3" t="n"/>
+      <c r="H745" s="3" t="n"/>
     </row>
     <row r="746">
       <c r="D746" s="2" t="n"/>
       <c r="F746" s="3" t="n"/>
+      <c r="H746" s="3" t="n"/>
     </row>
     <row r="747">
       <c r="D747" s="2" t="n"/>
       <c r="F747" s="3" t="n"/>
+      <c r="H747" s="3" t="n"/>
     </row>
     <row r="748">
       <c r="D748" s="2" t="n"/>
       <c r="F748" s="3" t="n"/>
+      <c r="H748" s="3" t="n"/>
     </row>
     <row r="749">
       <c r="D749" s="2" t="n"/>
       <c r="F749" s="3" t="n"/>
+      <c r="H749" s="3" t="n"/>
     </row>
     <row r="750">
       <c r="D750" s="2" t="n"/>
       <c r="F750" s="3" t="n"/>
+      <c r="H750" s="3" t="n"/>
     </row>
     <row r="751">
       <c r="D751" s="2" t="n"/>
       <c r="F751" s="3" t="n"/>
+      <c r="H751" s="3" t="n"/>
     </row>
     <row r="752">
       <c r="D752" s="2" t="n"/>
       <c r="F752" s="3" t="n"/>
+      <c r="H752" s="3" t="n"/>
     </row>
     <row r="753">
       <c r="D753" s="2" t="n"/>
       <c r="F753" s="3" t="n"/>
+      <c r="H753" s="3" t="n"/>
     </row>
     <row r="754">
       <c r="D754" s="2" t="n"/>
       <c r="F754" s="3" t="n"/>
+      <c r="H754" s="3" t="n"/>
     </row>
     <row r="755">
       <c r="D755" s="2" t="n"/>
       <c r="F755" s="3" t="n"/>
+      <c r="H755" s="3" t="n"/>
     </row>
     <row r="756">
       <c r="D756" s="2" t="n"/>
       <c r="F756" s="3" t="n"/>
+      <c r="H756" s="3" t="n"/>
     </row>
     <row r="757">
       <c r="D757" s="2" t="n"/>
       <c r="F757" s="3" t="n"/>
+      <c r="H757" s="3" t="n"/>
     </row>
     <row r="758">
       <c r="D758" s="2" t="n"/>
       <c r="F758" s="3" t="n"/>
+      <c r="H758" s="3" t="n"/>
     </row>
     <row r="759">
       <c r="D759" s="2" t="n"/>
       <c r="F759" s="3" t="n"/>
+      <c r="H759" s="3" t="n"/>
     </row>
     <row r="760">
       <c r="D760" s="2" t="n"/>
       <c r="F760" s="3" t="n"/>
+      <c r="H760" s="3" t="n"/>
     </row>
     <row r="761">
       <c r="D761" s="2" t="n"/>
       <c r="F761" s="3" t="n"/>
+      <c r="H761" s="3" t="n"/>
     </row>
     <row r="762">
       <c r="D762" s="2" t="n"/>
       <c r="F762" s="3" t="n"/>
+      <c r="H762" s="3" t="n"/>
     </row>
     <row r="763">
       <c r="D763" s="2" t="n"/>
       <c r="F763" s="3" t="n"/>
+      <c r="H763" s="3" t="n"/>
     </row>
     <row r="764">
       <c r="D764" s="2" t="n"/>
       <c r="F764" s="3" t="n"/>
+      <c r="H764" s="3" t="n"/>
     </row>
     <row r="765">
       <c r="D765" s="2" t="n"/>
       <c r="F765" s="3" t="n"/>
+      <c r="H765" s="3" t="n"/>
     </row>
     <row r="766">
       <c r="D766" s="2" t="n"/>
       <c r="F766" s="3" t="n"/>
+      <c r="H766" s="3" t="n"/>
     </row>
     <row r="767">
       <c r="D767" s="2" t="n"/>
       <c r="F767" s="3" t="n"/>
+      <c r="H767" s="3" t="n"/>
     </row>
     <row r="768">
       <c r="D768" s="2" t="n"/>
       <c r="F768" s="3" t="n"/>
+      <c r="H768" s="3" t="n"/>
     </row>
     <row r="769">
       <c r="D769" s="2" t="n"/>
       <c r="F769" s="3" t="n"/>
+      <c r="H769" s="3" t="n"/>
     </row>
     <row r="770">
       <c r="D770" s="2" t="n"/>
       <c r="F770" s="3" t="n"/>
+      <c r="H770" s="3" t="n"/>
     </row>
     <row r="771">
       <c r="D771" s="2" t="n"/>
       <c r="F771" s="3" t="n"/>
+      <c r="H771" s="3" t="n"/>
     </row>
     <row r="772">
       <c r="D772" s="2" t="n"/>
       <c r="F772" s="3" t="n"/>
+      <c r="H772" s="3" t="n"/>
     </row>
     <row r="773">
       <c r="D773" s="2" t="n"/>
       <c r="F773" s="3" t="n"/>
+      <c r="H773" s="3" t="n"/>
     </row>
     <row r="774">
       <c r="D774" s="2" t="n"/>
       <c r="F774" s="3" t="n"/>
+      <c r="H774" s="3" t="n"/>
     </row>
     <row r="775">
       <c r="D775" s="2" t="n"/>
       <c r="F775" s="3" t="n"/>
+      <c r="H775" s="3" t="n"/>
     </row>
     <row r="776">
       <c r="D776" s="2" t="n"/>
       <c r="F776" s="3" t="n"/>
+      <c r="H776" s="3" t="n"/>
     </row>
     <row r="777">
       <c r="D777" s="2" t="n"/>
       <c r="F777" s="3" t="n"/>
+      <c r="H777" s="3" t="n"/>
     </row>
     <row r="778">
       <c r="D778" s="2" t="n"/>
       <c r="F778" s="3" t="n"/>
+      <c r="H778" s="3" t="n"/>
     </row>
     <row r="779">
       <c r="D779" s="2" t="n"/>
       <c r="F779" s="3" t="n"/>
+      <c r="H779" s="3" t="n"/>
     </row>
     <row r="780">
       <c r="D780" s="2" t="n"/>
       <c r="F780" s="3" t="n"/>
+      <c r="H780" s="3" t="n"/>
     </row>
     <row r="781">
       <c r="D781" s="2" t="n"/>
       <c r="F781" s="3" t="n"/>
+      <c r="H781" s="3" t="n"/>
     </row>
     <row r="782">
       <c r="D782" s="2" t="n"/>
       <c r="F782" s="3" t="n"/>
+      <c r="H782" s="3" t="n"/>
     </row>
     <row r="783">
       <c r="D783" s="2" t="n"/>
       <c r="F783" s="3" t="n"/>
+      <c r="H783" s="3" t="n"/>
     </row>
     <row r="784">
       <c r="D784" s="2" t="n"/>
       <c r="F784" s="3" t="n"/>
+      <c r="H784" s="3" t="n"/>
     </row>
     <row r="785">
       <c r="D785" s="2" t="n"/>
       <c r="F785" s="3" t="n"/>
+      <c r="H785" s="3" t="n"/>
     </row>
     <row r="786">
       <c r="D786" s="2" t="n"/>
       <c r="F786" s="3" t="n"/>
+      <c r="H786" s="3" t="n"/>
     </row>
     <row r="787">
       <c r="D787" s="2" t="n"/>
       <c r="F787" s="3" t="n"/>
+      <c r="H787" s="3" t="n"/>
     </row>
     <row r="788">
       <c r="D788" s="2" t="n"/>
       <c r="F788" s="3" t="n"/>
+      <c r="H788" s="3" t="n"/>
     </row>
     <row r="789">
       <c r="D789" s="2" t="n"/>
       <c r="F789" s="3" t="n"/>
+      <c r="H789" s="3" t="n"/>
     </row>
     <row r="790">
       <c r="D790" s="2" t="n"/>
       <c r="F790" s="3" t="n"/>
+      <c r="H790" s="3" t="n"/>
     </row>
     <row r="791">
       <c r="D791" s="2" t="n"/>
       <c r="F791" s="3" t="n"/>
+      <c r="H791" s="3" t="n"/>
     </row>
     <row r="792">
       <c r="D792" s="2" t="n"/>
       <c r="F792" s="3" t="n"/>
+      <c r="H792" s="3" t="n"/>
     </row>
     <row r="793">
       <c r="D793" s="2" t="n"/>
       <c r="F793" s="3" t="n"/>
+      <c r="H793" s="3" t="n"/>
     </row>
     <row r="794">
       <c r="D794" s="2" t="n"/>
       <c r="F794" s="3" t="n"/>
+      <c r="H794" s="3" t="n"/>
     </row>
     <row r="795">
       <c r="D795" s="2" t="n"/>
       <c r="F795" s="3" t="n"/>
+      <c r="H795" s="3" t="n"/>
     </row>
     <row r="796">
       <c r="D796" s="2" t="n"/>
       <c r="F796" s="3" t="n"/>
+      <c r="H796" s="3" t="n"/>
     </row>
     <row r="797">
       <c r="D797" s="2" t="n"/>
       <c r="F797" s="3" t="n"/>
+      <c r="H797" s="3" t="n"/>
     </row>
     <row r="798">
       <c r="D798" s="2" t="n"/>
       <c r="F798" s="3" t="n"/>
+      <c r="H798" s="3" t="n"/>
     </row>
     <row r="799">
       <c r="D799" s="2" t="n"/>
       <c r="F799" s="3" t="n"/>
+      <c r="H799" s="3" t="n"/>
     </row>
     <row r="800">
       <c r="D800" s="2" t="n"/>
       <c r="F800" s="3" t="n"/>
+      <c r="H800" s="3" t="n"/>
     </row>
     <row r="801">
       <c r="D801" s="2" t="n"/>
       <c r="F801" s="3" t="n"/>
+      <c r="H801" s="3" t="n"/>
     </row>
     <row r="802">
       <c r="D802" s="2" t="n"/>
       <c r="F802" s="3" t="n"/>
+      <c r="H802" s="3" t="n"/>
     </row>
     <row r="803">
       <c r="D803" s="2" t="n"/>
       <c r="F803" s="3" t="n"/>
+      <c r="H803" s="3" t="n"/>
     </row>
     <row r="804">
       <c r="D804" s="2" t="n"/>
       <c r="F804" s="3" t="n"/>
+      <c r="H804" s="3" t="n"/>
     </row>
     <row r="805">
       <c r="D805" s="2" t="n"/>
       <c r="F805" s="3" t="n"/>
+      <c r="H805" s="3" t="n"/>
     </row>
     <row r="806">
       <c r="D806" s="2" t="n"/>
       <c r="F806" s="3" t="n"/>
+      <c r="H806" s="3" t="n"/>
     </row>
     <row r="807">
       <c r="D807" s="2" t="n"/>
       <c r="F807" s="3" t="n"/>
+      <c r="H807" s="3" t="n"/>
     </row>
     <row r="808">
       <c r="D808" s="2" t="n"/>
       <c r="F808" s="3" t="n"/>
+      <c r="H808" s="3" t="n"/>
     </row>
     <row r="809">
       <c r="D809" s="2" t="n"/>
       <c r="F809" s="3" t="n"/>
+      <c r="H809" s="3" t="n"/>
     </row>
     <row r="810">
       <c r="D810" s="2" t="n"/>
       <c r="F810" s="3" t="n"/>
+      <c r="H810" s="3" t="n"/>
     </row>
     <row r="811">
       <c r="D811" s="2" t="n"/>
       <c r="F811" s="3" t="n"/>
+      <c r="H811" s="3" t="n"/>
     </row>
     <row r="812">
       <c r="D812" s="2" t="n"/>
       <c r="F812" s="3" t="n"/>
+      <c r="H812" s="3" t="n"/>
     </row>
     <row r="813">
       <c r="D813" s="2" t="n"/>
       <c r="F813" s="3" t="n"/>
+      <c r="H813" s="3" t="n"/>
     </row>
     <row r="814">
       <c r="D814" s="2" t="n"/>
       <c r="F814" s="3" t="n"/>
+      <c r="H814" s="3" t="n"/>
     </row>
     <row r="815">
       <c r="D815" s="2" t="n"/>
       <c r="F815" s="3" t="n"/>
+      <c r="H815" s="3" t="n"/>
     </row>
     <row r="816">
       <c r="D816" s="2" t="n"/>
       <c r="F816" s="3" t="n"/>
+      <c r="H816" s="3" t="n"/>
     </row>
     <row r="817">
       <c r="D817" s="2" t="n"/>
       <c r="F817" s="3" t="n"/>
+      <c r="H817" s="3" t="n"/>
     </row>
     <row r="818">
       <c r="D818" s="2" t="n"/>
       <c r="F818" s="3" t="n"/>
+      <c r="H818" s="3" t="n"/>
     </row>
     <row r="819">
       <c r="D819" s="2" t="n"/>
       <c r="F819" s="3" t="n"/>
+      <c r="H819" s="3" t="n"/>
     </row>
     <row r="820">
       <c r="D820" s="2" t="n"/>
       <c r="F820" s="3" t="n"/>
+      <c r="H820" s="3" t="n"/>
     </row>
     <row r="821">
       <c r="D821" s="2" t="n"/>
       <c r="F821" s="3" t="n"/>
+      <c r="H821" s="3" t="n"/>
     </row>
     <row r="822">
       <c r="D822" s="2" t="n"/>
       <c r="F822" s="3" t="n"/>
+      <c r="H822" s="3" t="n"/>
     </row>
     <row r="823">
       <c r="D823" s="2" t="n"/>
       <c r="F823" s="3" t="n"/>
+      <c r="H823" s="3" t="n"/>
     </row>
     <row r="824">
       <c r="D824" s="2" t="n"/>
       <c r="F824" s="3" t="n"/>
+      <c r="H824" s="3" t="n"/>
     </row>
     <row r="825">
       <c r="D825" s="2" t="n"/>
       <c r="F825" s="3" t="n"/>
+      <c r="H825" s="3" t="n"/>
     </row>
     <row r="826">
       <c r="D826" s="2" t="n"/>
       <c r="F826" s="3" t="n"/>
+      <c r="H826" s="3" t="n"/>
     </row>
     <row r="827">
       <c r="D827" s="2" t="n"/>
       <c r="F827" s="3" t="n"/>
+      <c r="H827" s="3" t="n"/>
     </row>
     <row r="828">
       <c r="D828" s="2" t="n"/>
       <c r="F828" s="3" t="n"/>
+      <c r="H828" s="3" t="n"/>
     </row>
     <row r="829">
       <c r="D829" s="2" t="n"/>
       <c r="F829" s="3" t="n"/>
+      <c r="H829" s="3" t="n"/>
     </row>
     <row r="830">
       <c r="D830" s="2" t="n"/>
       <c r="F830" s="3" t="n"/>
+      <c r="H830" s="3" t="n"/>
     </row>
     <row r="831">
       <c r="D831" s="2" t="n"/>
       <c r="F831" s="3" t="n"/>
+      <c r="H831" s="3" t="n"/>
     </row>
     <row r="832">
       <c r="D832" s="2" t="n"/>
       <c r="F832" s="3" t="n"/>
+      <c r="H832" s="3" t="n"/>
     </row>
     <row r="833">
       <c r="D833" s="2" t="n"/>
       <c r="F833" s="3" t="n"/>
+      <c r="H833" s="3" t="n"/>
     </row>
     <row r="834">
       <c r="D834" s="2" t="n"/>
       <c r="F834" s="3" t="n"/>
+      <c r="H834" s="3" t="n"/>
     </row>
     <row r="835">
       <c r="D835" s="2" t="n"/>
       <c r="F835" s="3" t="n"/>
+      <c r="H835" s="3" t="n"/>
     </row>
     <row r="836">
       <c r="D836" s="2" t="n"/>
       <c r="F836" s="3" t="n"/>
+      <c r="H836" s="3" t="n"/>
     </row>
     <row r="837">
       <c r="D837" s="2" t="n"/>
       <c r="F837" s="3" t="n"/>
+      <c r="H837" s="3" t="n"/>
     </row>
     <row r="838">
       <c r="D838" s="2" t="n"/>
       <c r="F838" s="3" t="n"/>
+      <c r="H838" s="3" t="n"/>
     </row>
     <row r="839">
       <c r="D839" s="2" t="n"/>
       <c r="F839" s="3" t="n"/>
+      <c r="H839" s="3" t="n"/>
     </row>
     <row r="840">
       <c r="D840" s="2" t="n"/>
       <c r="F840" s="3" t="n"/>
+      <c r="H840" s="3" t="n"/>
     </row>
     <row r="841">
       <c r="D841" s="2" t="n"/>
       <c r="F841" s="3" t="n"/>
+      <c r="H841" s="3" t="n"/>
     </row>
     <row r="842">
       <c r="D842" s="2" t="n"/>
       <c r="F842" s="3" t="n"/>
+      <c r="H842" s="3" t="n"/>
     </row>
     <row r="843">
       <c r="D843" s="2" t="n"/>
       <c r="F843" s="3" t="n"/>
+      <c r="H843" s="3" t="n"/>
     </row>
     <row r="844">
       <c r="D844" s="2" t="n"/>
       <c r="F844" s="3" t="n"/>
+      <c r="H844" s="3" t="n"/>
     </row>
     <row r="845">
       <c r="D845" s="2" t="n"/>
       <c r="F845" s="3" t="n"/>
+      <c r="H845" s="3" t="n"/>
     </row>
     <row r="846">
       <c r="D846" s="2" t="n"/>
       <c r="F846" s="3" t="n"/>
+      <c r="H846" s="3" t="n"/>
     </row>
     <row r="847">
       <c r="D847" s="2" t="n"/>
       <c r="F847" s="3" t="n"/>
+      <c r="H847" s="3" t="n"/>
     </row>
     <row r="848">
       <c r="D848" s="2" t="n"/>
       <c r="F848" s="3" t="n"/>
+      <c r="H848" s="3" t="n"/>
     </row>
     <row r="849">
       <c r="D849" s="2" t="n"/>
       <c r="F849" s="3" t="n"/>
+      <c r="H849" s="3" t="n"/>
     </row>
     <row r="850">
       <c r="D850" s="2" t="n"/>
       <c r="F850" s="3" t="n"/>
+      <c r="H850" s="3" t="n"/>
     </row>
     <row r="851">
       <c r="D851" s="2" t="n"/>
       <c r="F851" s="3" t="n"/>
+      <c r="H851" s="3" t="n"/>
     </row>
     <row r="852">
       <c r="D852" s="2" t="n"/>
       <c r="F852" s="3" t="n"/>
+      <c r="H852" s="3" t="n"/>
     </row>
     <row r="853">
       <c r="D853" s="2" t="n"/>
       <c r="F853" s="3" t="n"/>
+      <c r="H853" s="3" t="n"/>
     </row>
     <row r="854">
       <c r="D854" s="2" t="n"/>
       <c r="F854" s="3" t="n"/>
+      <c r="H854" s="3" t="n"/>
     </row>
     <row r="855">
       <c r="D855" s="2" t="n"/>
       <c r="F855" s="3" t="n"/>
+      <c r="H855" s="3" t="n"/>
     </row>
     <row r="856">
       <c r="D856" s="2" t="n"/>
       <c r="F856" s="3" t="n"/>
+      <c r="H856" s="3" t="n"/>
     </row>
     <row r="857">
       <c r="D857" s="2" t="n"/>
       <c r="F857" s="3" t="n"/>
+      <c r="H857" s="3" t="n"/>
     </row>
     <row r="858">
       <c r="D858" s="2" t="n"/>
       <c r="F858" s="3" t="n"/>
+      <c r="H858" s="3" t="n"/>
     </row>
     <row r="859">
       <c r="D859" s="2" t="n"/>
       <c r="F859" s="3" t="n"/>
+      <c r="H859" s="3" t="n"/>
     </row>
     <row r="860">
       <c r="D860" s="2" t="n"/>
       <c r="F860" s="3" t="n"/>
+      <c r="H860" s="3" t="n"/>
     </row>
     <row r="861">
       <c r="D861" s="2" t="n"/>
       <c r="F861" s="3" t="n"/>
+      <c r="H861" s="3" t="n"/>
     </row>
     <row r="862">
       <c r="D862" s="2" t="n"/>
       <c r="F862" s="3" t="n"/>
+      <c r="H862" s="3" t="n"/>
     </row>
     <row r="863">
       <c r="D863" s="2" t="n"/>
       <c r="F863" s="3" t="n"/>
+      <c r="H863" s="3" t="n"/>
     </row>
     <row r="864">
       <c r="D864" s="2" t="n"/>
       <c r="F864" s="3" t="n"/>
+      <c r="H864" s="3" t="n"/>
     </row>
     <row r="865">
       <c r="D865" s="2" t="n"/>
       <c r="F865" s="3" t="n"/>
+      <c r="H865" s="3" t="n"/>
     </row>
     <row r="866">
       <c r="D866" s="2" t="n"/>
       <c r="F866" s="3" t="n"/>
+      <c r="H866" s="3" t="n"/>
     </row>
     <row r="867">
       <c r="D867" s="2" t="n"/>
       <c r="F867" s="3" t="n"/>
+      <c r="H867" s="3" t="n"/>
     </row>
     <row r="868">
       <c r="D868" s="2" t="n"/>
       <c r="F868" s="3" t="n"/>
+      <c r="H868" s="3" t="n"/>
     </row>
     <row r="869">
       <c r="D869" s="2" t="n"/>
       <c r="F869" s="3" t="n"/>
+      <c r="H869" s="3" t="n"/>
     </row>
     <row r="870">
       <c r="D870" s="2" t="n"/>
       <c r="F870" s="3" t="n"/>
+      <c r="H870" s="3" t="n"/>
     </row>
     <row r="871">
       <c r="D871" s="2" t="n"/>
       <c r="F871" s="3" t="n"/>
+      <c r="H871" s="3" t="n"/>
     </row>
     <row r="872">
       <c r="D872" s="2" t="n"/>
       <c r="F872" s="3" t="n"/>
+      <c r="H872" s="3" t="n"/>
     </row>
     <row r="873">
       <c r="D873" s="2" t="n"/>
       <c r="F873" s="3" t="n"/>
+      <c r="H873" s="3" t="n"/>
     </row>
     <row r="874">
       <c r="D874" s="2" t="n"/>
       <c r="F874" s="3" t="n"/>
+      <c r="H874" s="3" t="n"/>
     </row>
     <row r="875">
       <c r="D875" s="2" t="n"/>
       <c r="F875" s="3" t="n"/>
+      <c r="H875" s="3" t="n"/>
     </row>
     <row r="876">
       <c r="D876" s="2" t="n"/>
       <c r="F876" s="3" t="n"/>
+      <c r="H876" s="3" t="n"/>
     </row>
     <row r="877">
       <c r="D877" s="2" t="n"/>
       <c r="F877" s="3" t="n"/>
+      <c r="H877" s="3" t="n"/>
     </row>
     <row r="878">
       <c r="D878" s="2" t="n"/>
       <c r="F878" s="3" t="n"/>
+      <c r="H878" s="3" t="n"/>
     </row>
     <row r="879">
       <c r="D879" s="2" t="n"/>
       <c r="F879" s="3" t="n"/>
+      <c r="H879" s="3" t="n"/>
     </row>
     <row r="880">
       <c r="D880" s="2" t="n"/>
       <c r="F880" s="3" t="n"/>
+      <c r="H880" s="3" t="n"/>
     </row>
     <row r="881">
       <c r="D881" s="2" t="n"/>
       <c r="F881" s="3" t="n"/>
+      <c r="H881" s="3" t="n"/>
     </row>
     <row r="882">
       <c r="D882" s="2" t="n"/>
       <c r="F882" s="3" t="n"/>
+      <c r="H882" s="3" t="n"/>
     </row>
     <row r="883">
       <c r="D883" s="2" t="n"/>
       <c r="F883" s="3" t="n"/>
+      <c r="H883" s="3" t="n"/>
     </row>
     <row r="884">
       <c r="D884" s="2" t="n"/>
       <c r="F884" s="3" t="n"/>
+      <c r="H884" s="3" t="n"/>
     </row>
     <row r="885">
       <c r="D885" s="2" t="n"/>
       <c r="F885" s="3" t="n"/>
+      <c r="H885" s="3" t="n"/>
     </row>
     <row r="886">
       <c r="D886" s="2" t="n"/>
       <c r="F886" s="3" t="n"/>
+      <c r="H886" s="3" t="n"/>
     </row>
     <row r="887">
       <c r="D887" s="2" t="n"/>
       <c r="F887" s="3" t="n"/>
+      <c r="H887" s="3" t="n"/>
     </row>
     <row r="888">
       <c r="D888" s="2" t="n"/>
       <c r="F888" s="3" t="n"/>
+      <c r="H888" s="3" t="n"/>
     </row>
     <row r="889">
       <c r="D889" s="2" t="n"/>
       <c r="F889" s="3" t="n"/>
+      <c r="H889" s="3" t="n"/>
     </row>
     <row r="890">
       <c r="D890" s="2" t="n"/>
       <c r="F890" s="3" t="n"/>
+      <c r="H890" s="3" t="n"/>
     </row>
     <row r="891">
       <c r="D891" s="2" t="n"/>
       <c r="F891" s="3" t="n"/>
+      <c r="H891" s="3" t="n"/>
     </row>
     <row r="892">
       <c r="D892" s="2" t="n"/>
       <c r="F892" s="3" t="n"/>
+      <c r="H892" s="3" t="n"/>
     </row>
     <row r="893">
       <c r="D893" s="2" t="n"/>
       <c r="F893" s="3" t="n"/>
+      <c r="H893" s="3" t="n"/>
     </row>
     <row r="894">
       <c r="D894" s="2" t="n"/>
       <c r="F894" s="3" t="n"/>
+      <c r="H894" s="3" t="n"/>
     </row>
     <row r="895">
       <c r="D895" s="2" t="n"/>
       <c r="F895" s="3" t="n"/>
+      <c r="H895" s="3" t="n"/>
     </row>
     <row r="896">
       <c r="D896" s="2" t="n"/>
       <c r="F896" s="3" t="n"/>
+      <c r="H896" s="3" t="n"/>
     </row>
     <row r="897">
       <c r="D897" s="2" t="n"/>
       <c r="F897" s="3" t="n"/>
+      <c r="H897" s="3" t="n"/>
     </row>
     <row r="898">
       <c r="D898" s="2" t="n"/>
       <c r="F898" s="3" t="n"/>
+      <c r="H898" s="3" t="n"/>
     </row>
     <row r="899">
       <c r="D899" s="2" t="n"/>
       <c r="F899" s="3" t="n"/>
+      <c r="H899" s="3" t="n"/>
     </row>
     <row r="900">
       <c r="D900" s="2" t="n"/>
       <c r="F900" s="3" t="n"/>
+      <c r="H900" s="3" t="n"/>
     </row>
     <row r="901">
       <c r="D901" s="2" t="n"/>
       <c r="F901" s="3" t="n"/>
+      <c r="H901" s="3" t="n"/>
     </row>
     <row r="902">
       <c r="D902" s="2" t="n"/>
       <c r="F902" s="3" t="n"/>
+      <c r="H902" s="3" t="n"/>
     </row>
     <row r="903">
       <c r="D903" s="2" t="n"/>
       <c r="F903" s="3" t="n"/>
+      <c r="H903" s="3" t="n"/>
     </row>
     <row r="904">
       <c r="D904" s="2" t="n"/>
       <c r="F904" s="3" t="n"/>
+      <c r="H904" s="3" t="n"/>
     </row>
     <row r="905">
       <c r="D905" s="2" t="n"/>
       <c r="F905" s="3" t="n"/>
+      <c r="H905" s="3" t="n"/>
     </row>
     <row r="906">
       <c r="D906" s="2" t="n"/>
       <c r="F906" s="3" t="n"/>
+      <c r="H906" s="3" t="n"/>
     </row>
     <row r="907">
       <c r="D907" s="2" t="n"/>
       <c r="F907" s="3" t="n"/>
+      <c r="H907" s="3" t="n"/>
     </row>
     <row r="908">
       <c r="D908" s="2" t="n"/>
       <c r="F908" s="3" t="n"/>
+      <c r="H908" s="3" t="n"/>
     </row>
     <row r="909">
       <c r="D909" s="2" t="n"/>
       <c r="F909" s="3" t="n"/>
+      <c r="H909" s="3" t="n"/>
     </row>
     <row r="910">
       <c r="D910" s="2" t="n"/>
       <c r="F910" s="3" t="n"/>
+      <c r="H910" s="3" t="n"/>
     </row>
     <row r="911">
       <c r="D911" s="2" t="n"/>
       <c r="F911" s="3" t="n"/>
+      <c r="H911" s="3" t="n"/>
     </row>
     <row r="912">
       <c r="D912" s="2" t="n"/>
       <c r="F912" s="3" t="n"/>
+      <c r="H912" s="3" t="n"/>
     </row>
     <row r="913">
       <c r="D913" s="2" t="n"/>
       <c r="F913" s="3" t="n"/>
+      <c r="H913" s="3" t="n"/>
     </row>
     <row r="914">
       <c r="D914" s="2" t="n"/>
       <c r="F914" s="3" t="n"/>
+      <c r="H914" s="3" t="n"/>
     </row>
     <row r="915">
       <c r="D915" s="2" t="n"/>
       <c r="F915" s="3" t="n"/>
+      <c r="H915" s="3" t="n"/>
     </row>
     <row r="916">
       <c r="D916" s="2" t="n"/>
       <c r="F916" s="3" t="n"/>
+      <c r="H916" s="3" t="n"/>
     </row>
     <row r="917">
       <c r="D917" s="2" t="n"/>
       <c r="F917" s="3" t="n"/>
+      <c r="H917" s="3" t="n"/>
     </row>
     <row r="918">
       <c r="D918" s="2" t="n"/>
       <c r="F918" s="3" t="n"/>
+      <c r="H918" s="3" t="n"/>
     </row>
     <row r="919">
       <c r="D919" s="2" t="n"/>
       <c r="F919" s="3" t="n"/>
+      <c r="H919" s="3" t="n"/>
     </row>
     <row r="920">
       <c r="D920" s="2" t="n"/>
       <c r="F920" s="3" t="n"/>
+      <c r="H920" s="3" t="n"/>
     </row>
     <row r="921">
       <c r="D921" s="2" t="n"/>
       <c r="F921" s="3" t="n"/>
+      <c r="H921" s="3" t="n"/>
     </row>
     <row r="922">
       <c r="D922" s="2" t="n"/>
       <c r="F922" s="3" t="n"/>
+      <c r="H922" s="3" t="n"/>
     </row>
     <row r="923">
       <c r="D923" s="2" t="n"/>
       <c r="F923" s="3" t="n"/>
+      <c r="H923" s="3" t="n"/>
     </row>
     <row r="924">
       <c r="D924" s="2" t="n"/>
       <c r="F924" s="3" t="n"/>
+      <c r="H924" s="3" t="n"/>
     </row>
     <row r="925">
       <c r="D925" s="2" t="n"/>
       <c r="F925" s="3" t="n"/>
+      <c r="H925" s="3" t="n"/>
     </row>
     <row r="926">
       <c r="D926" s="2" t="n"/>
       <c r="F926" s="3" t="n"/>
+      <c r="H926" s="3" t="n"/>
     </row>
     <row r="927">
       <c r="D927" s="2" t="n"/>
       <c r="F927" s="3" t="n"/>
+      <c r="H927" s="3" t="n"/>
     </row>
     <row r="928">
       <c r="D928" s="2" t="n"/>
       <c r="F928" s="3" t="n"/>
+      <c r="H928" s="3" t="n"/>
     </row>
     <row r="929">
       <c r="D929" s="2" t="n"/>
       <c r="F929" s="3" t="n"/>
+      <c r="H929" s="3" t="n"/>
     </row>
     <row r="930">
       <c r="D930" s="2" t="n"/>
       <c r="F930" s="3" t="n"/>
+      <c r="H930" s="3" t="n"/>
     </row>
     <row r="931">
       <c r="D931" s="2" t="n"/>
       <c r="F931" s="3" t="n"/>
+      <c r="H931" s="3" t="n"/>
     </row>
     <row r="932">
       <c r="D932" s="2" t="n"/>
       <c r="F932" s="3" t="n"/>
+      <c r="H932" s="3" t="n"/>
     </row>
     <row r="933">
       <c r="D933" s="2" t="n"/>
       <c r="F933" s="3" t="n"/>
+      <c r="H933" s="3" t="n"/>
     </row>
     <row r="934">
       <c r="D934" s="2" t="n"/>
       <c r="F934" s="3" t="n"/>
+      <c r="H934" s="3" t="n"/>
     </row>
     <row r="935">
       <c r="D935" s="2" t="n"/>
       <c r="F935" s="3" t="n"/>
+      <c r="H935" s="3" t="n"/>
     </row>
     <row r="936">
       <c r="D936" s="2" t="n"/>
       <c r="F936" s="3" t="n"/>
+      <c r="H936" s="3" t="n"/>
     </row>
     <row r="937">
       <c r="D937" s="2" t="n"/>
       <c r="F937" s="3" t="n"/>
+      <c r="H937" s="3" t="n"/>
     </row>
     <row r="938">
       <c r="D938" s="2" t="n"/>
       <c r="F938" s="3" t="n"/>
+      <c r="H938" s="3" t="n"/>
     </row>
     <row r="939">
       <c r="D939" s="2" t="n"/>
       <c r="F939" s="3" t="n"/>
+      <c r="H939" s="3" t="n"/>
     </row>
     <row r="940">
       <c r="D940" s="2" t="n"/>
       <c r="F940" s="3" t="n"/>
+      <c r="H940" s="3" t="n"/>
     </row>
     <row r="941">
       <c r="D941" s="2" t="n"/>
       <c r="F941" s="3" t="n"/>
+      <c r="H941" s="3" t="n"/>
     </row>
     <row r="942">
       <c r="D942" s="2" t="n"/>
       <c r="F942" s="3" t="n"/>
+      <c r="H942" s="3" t="n"/>
     </row>
     <row r="943">
       <c r="D943" s="2" t="n"/>
       <c r="F943" s="3" t="n"/>
+      <c r="H943" s="3" t="n"/>
     </row>
     <row r="944">
       <c r="D944" s="2" t="n"/>
       <c r="F944" s="3" t="n"/>
+      <c r="H944" s="3" t="n"/>
     </row>
     <row r="945">
       <c r="D945" s="2" t="n"/>
       <c r="F945" s="3" t="n"/>
+      <c r="H945" s="3" t="n"/>
     </row>
     <row r="946">
       <c r="D946" s="2" t="n"/>
       <c r="F946" s="3" t="n"/>
+      <c r="H946" s="3" t="n"/>
     </row>
     <row r="947">
       <c r="D947" s="2" t="n"/>
       <c r="F947" s="3" t="n"/>
+      <c r="H947" s="3" t="n"/>
     </row>
     <row r="948">
       <c r="D948" s="2" t="n"/>
       <c r="F948" s="3" t="n"/>
+      <c r="H948" s="3" t="n"/>
     </row>
     <row r="949">
       <c r="D949" s="2" t="n"/>
       <c r="F949" s="3" t="n"/>
+      <c r="H949" s="3" t="n"/>
     </row>
     <row r="950">
       <c r="D950" s="2" t="n"/>
       <c r="F950" s="3" t="n"/>
+      <c r="H950" s="3" t="n"/>
     </row>
     <row r="951">
       <c r="D951" s="2" t="n"/>
       <c r="F951" s="3" t="n"/>
+      <c r="H951" s="3" t="n"/>
     </row>
     <row r="952">
       <c r="D952" s="2" t="n"/>
       <c r="F952" s="3" t="n"/>
+      <c r="H952" s="3" t="n"/>
     </row>
     <row r="953">
       <c r="D953" s="2" t="n"/>
       <c r="F953" s="3" t="n"/>
+      <c r="H953" s="3" t="n"/>
     </row>
     <row r="954">
       <c r="D954" s="2" t="n"/>
       <c r="F954" s="3" t="n"/>
+      <c r="H954" s="3" t="n"/>
     </row>
     <row r="955">
       <c r="D955" s="2" t="n"/>
       <c r="F955" s="3" t="n"/>
+      <c r="H955" s="3" t="n"/>
     </row>
     <row r="956">
       <c r="D956" s="2" t="n"/>
       <c r="F956" s="3" t="n"/>
+      <c r="H956" s="3" t="n"/>
     </row>
     <row r="957">
       <c r="D957" s="2" t="n"/>
       <c r="F957" s="3" t="n"/>
+      <c r="H957" s="3" t="n"/>
     </row>
     <row r="958">
       <c r="D958" s="2" t="n"/>
       <c r="F958" s="3" t="n"/>
+      <c r="H958" s="3" t="n"/>
     </row>
     <row r="959">
       <c r="D959" s="2" t="n"/>
       <c r="F959" s="3" t="n"/>
+      <c r="H959" s="3" t="n"/>
     </row>
     <row r="960">
       <c r="D960" s="2" t="n"/>
       <c r="F960" s="3" t="n"/>
+      <c r="H960" s="3" t="n"/>
     </row>
     <row r="961">
       <c r="D961" s="2" t="n"/>
       <c r="F961" s="3" t="n"/>
+      <c r="H961" s="3" t="n"/>
     </row>
     <row r="962">
       <c r="D962" s="2" t="n"/>
       <c r="F962" s="3" t="n"/>
+      <c r="H962" s="3" t="n"/>
     </row>
     <row r="963">
       <c r="D963" s="2" t="n"/>
       <c r="F963" s="3" t="n"/>
+      <c r="H963" s="3" t="n"/>
     </row>
     <row r="964">
       <c r="D964" s="2" t="n"/>
       <c r="F964" s="3" t="n"/>
+      <c r="H964" s="3" t="n"/>
     </row>
     <row r="965">
       <c r="D965" s="2" t="n"/>
       <c r="F965" s="3" t="n"/>
+      <c r="H965" s="3" t="n"/>
     </row>
     <row r="966">
       <c r="D966" s="2" t="n"/>
       <c r="F966" s="3" t="n"/>
+      <c r="H966" s="3" t="n"/>
     </row>
     <row r="967">
       <c r="D967" s="2" t="n"/>
       <c r="F967" s="3" t="n"/>
+      <c r="H967" s="3" t="n"/>
     </row>
     <row r="968">
       <c r="D968" s="2" t="n"/>
       <c r="F968" s="3" t="n"/>
+      <c r="H968" s="3" t="n"/>
     </row>
     <row r="969">
       <c r="D969" s="2" t="n"/>
       <c r="F969" s="3" t="n"/>
+      <c r="H969" s="3" t="n"/>
     </row>
     <row r="970">
       <c r="D970" s="2" t="n"/>
       <c r="F970" s="3" t="n"/>
+      <c r="H970" s="3" t="n"/>
     </row>
     <row r="971">
       <c r="D971" s="2" t="n"/>
       <c r="F971" s="3" t="n"/>
+      <c r="H971" s="3" t="n"/>
     </row>
     <row r="972">
       <c r="D972" s="2" t="n"/>
       <c r="F972" s="3" t="n"/>
+      <c r="H972" s="3" t="n"/>
     </row>
     <row r="973">
       <c r="D973" s="2" t="n"/>
       <c r="F973" s="3" t="n"/>
+      <c r="H973" s="3" t="n"/>
     </row>
     <row r="974">
       <c r="D974" s="2" t="n"/>
       <c r="F974" s="3" t="n"/>
+      <c r="H974" s="3" t="n"/>
     </row>
     <row r="975">
       <c r="D975" s="2" t="n"/>
       <c r="F975" s="3" t="n"/>
+      <c r="H975" s="3" t="n"/>
     </row>
     <row r="976">
       <c r="D976" s="2" t="n"/>
       <c r="F976" s="3" t="n"/>
+      <c r="H976" s="3" t="n"/>
     </row>
     <row r="977">
       <c r="D977" s="2" t="n"/>
       <c r="F977" s="3" t="n"/>
+      <c r="H977" s="3" t="n"/>
     </row>
     <row r="978">
       <c r="D978" s="2" t="n"/>
       <c r="F978" s="3" t="n"/>
+      <c r="H978" s="3" t="n"/>
     </row>
     <row r="979">
       <c r="D979" s="2" t="n"/>
       <c r="F979" s="3" t="n"/>
+      <c r="H979" s="3" t="n"/>
     </row>
     <row r="980">
       <c r="D980" s="2" t="n"/>
       <c r="F980" s="3" t="n"/>
+      <c r="H980" s="3" t="n"/>
     </row>
     <row r="981">
       <c r="D981" s="2" t="n"/>
       <c r="F981" s="3" t="n"/>
+      <c r="H981" s="3" t="n"/>
     </row>
     <row r="982">
       <c r="D982" s="2" t="n"/>
       <c r="F982" s="3" t="n"/>
+      <c r="H982" s="3" t="n"/>
     </row>
     <row r="983">
       <c r="D983" s="2" t="n"/>
       <c r="F983" s="3" t="n"/>
+      <c r="H983" s="3" t="n"/>
     </row>
     <row r="984">
       <c r="D984" s="2" t="n"/>
       <c r="F984" s="3" t="n"/>
+      <c r="H984" s="3" t="n"/>
     </row>
     <row r="985">
       <c r="D985" s="2" t="n"/>
       <c r="F985" s="3" t="n"/>
+      <c r="H985" s="3" t="n"/>
     </row>
     <row r="986">
       <c r="D986" s="2" t="n"/>
       <c r="F986" s="3" t="n"/>
+      <c r="H986" s="3" t="n"/>
     </row>
     <row r="987">
       <c r="D987" s="2" t="n"/>
       <c r="F987" s="3" t="n"/>
+      <c r="H987" s="3" t="n"/>
     </row>
     <row r="988">
       <c r="D988" s="2" t="n"/>
       <c r="F988" s="3" t="n"/>
+      <c r="H988" s="3" t="n"/>
     </row>
     <row r="989">
       <c r="D989" s="2" t="n"/>
       <c r="F989" s="3" t="n"/>
+      <c r="H989" s="3" t="n"/>
     </row>
     <row r="990">
       <c r="D990" s="2" t="n"/>
       <c r="F990" s="3" t="n"/>
+      <c r="H990" s="3" t="n"/>
     </row>
     <row r="991">
       <c r="D991" s="2" t="n"/>
       <c r="F991" s="3" t="n"/>
+      <c r="H991" s="3" t="n"/>
     </row>
     <row r="992">
       <c r="D992" s="2" t="n"/>
       <c r="F992" s="3" t="n"/>
+      <c r="H992" s="3" t="n"/>
     </row>
     <row r="993">
       <c r="D993" s="2" t="n"/>
       <c r="F993" s="3" t="n"/>
+      <c r="H993" s="3" t="n"/>
     </row>
     <row r="994">
       <c r="D994" s="2" t="n"/>
       <c r="F994" s="3" t="n"/>
+      <c r="H994" s="3" t="n"/>
     </row>
     <row r="995">
       <c r="D995" s="2" t="n"/>
       <c r="F995" s="3" t="n"/>
+      <c r="H995" s="3" t="n"/>
     </row>
     <row r="996">
       <c r="D996" s="2" t="n"/>
       <c r="F996" s="3" t="n"/>
+      <c r="H996" s="3" t="n"/>
     </row>
     <row r="997">
       <c r="D997" s="2" t="n"/>
       <c r="F997" s="3" t="n"/>
+      <c r="H997" s="3" t="n"/>
     </row>
     <row r="998">
       <c r="D998" s="2" t="n"/>
       <c r="F998" s="3" t="n"/>
+      <c r="H998" s="3" t="n"/>
     </row>
     <row r="999">
       <c r="D999" s="2" t="n"/>
       <c r="F999" s="3" t="n"/>
+      <c r="H999" s="3" t="n"/>
     </row>
     <row r="1000">
       <c r="D1000" s="2" t="n"/>
       <c r="F1000" s="3" t="n"/>
+      <c r="H1000" s="3" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Fijo,Variable"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8527,7 +9543,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Extra,Prima,Bonificación,Renta,Otro"</formula1>
+      <formula1>"Salario,Extra,Prima,Bonificación,Renta,Otro"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
